--- a/research/traditional_assets/database/data/cayman_islands/cayman_islands_telecom_equipment.xlsx
+++ b/research/traditional_assets/database/data/cayman_islands/cayman_islands_telecom_equipment.xlsx
@@ -1261,43 +1261,43 @@
         <v>94.8818897637795</v>
       </c>
       <c r="F2">
-        <v>10000000</v>
+        <v>85.9109285474173</v>
       </c>
       <c r="G2">
         <v>0.759868421052632</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>0.183453947368421</v>
       </c>
       <c r="I2">
         <v>0.0414201183431953</v>
       </c>
       <c r="J2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="K2">
         <v>534.6</v>
       </c>
       <c r="L2">
-        <v>563.097442234905</v>
+        <v>557.136819721995</v>
       </c>
       <c r="M2">
         <v>507.8</v>
       </c>
       <c r="N2">
-        <v>513.197442234905</v>
+        <v>512.8138197219949</v>
       </c>
       <c r="O2">
         <v>23.1</v>
       </c>
       <c r="P2">
-        <v>0</v>
+        <v>5.577</v>
       </c>
       <c r="Q2">
         <v>0.106593890228676</v>
       </c>
       <c r="R2">
-        <v>0.105954503739696</v>
+        <v>0.105999503739696</v>
       </c>
       <c r="S2">
         <v>0.0612366166625341</v>
@@ -1319,13 +1319,13 @@
         <v>0.108553772419806</v>
       </c>
       <c r="X2">
-        <v>0.105954503739696</v>
+        <v>0.106562124989592</v>
       </c>
       <c r="Y2">
         <v>1.2231878279972</v>
       </c>
       <c r="Z2">
-        <v>1.1725232434056</v>
+        <v>1.18436691253091</v>
       </c>
       <c r="AA2">
         <v>23.1</v>
@@ -1406,7 +1406,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1543,22 +1543,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1059545037396958</v>
+        <v>0.1059995037396958</v>
       </c>
       <c r="C2">
-        <v>563.0974422349054</v>
+        <v>557.1368197219952</v>
       </c>
       <c r="D2">
-        <v>513.1974422349055</v>
+        <v>512.8138197219952</v>
       </c>
       <c r="E2">
-        <v>-23.1</v>
+        <v>-17.523</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>5.577000000000001</v>
       </c>
       <c r="G2">
         <v>49.9</v>
@@ -1579,28 +1579,28 @@
         <v>24.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.2805231</v>
       </c>
       <c r="N2">
-        <v>24.1</v>
+        <v>23.8194769</v>
       </c>
       <c r="O2">
         <v>0</v>
       </c>
       <c r="P2">
-        <v>24.1</v>
+        <v>23.8194769</v>
       </c>
       <c r="Q2">
-        <v>30.4</v>
+        <v>30.1194769</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1059545037396958</v>
+        <v>0.1065621249895917</v>
       </c>
       <c r="T2">
-        <v>1.172523243405601</v>
+        <v>1.184366912530911</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1617,7 +1617,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>85.9109285474173</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1625,22 +1625,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1059995037396958</v>
+        <v>0.1060445037396957</v>
       </c>
       <c r="C3">
-        <v>557.1368197219952</v>
+        <v>551.1767703074429</v>
       </c>
       <c r="D3">
-        <v>512.8138197219952</v>
+        <v>512.4307703074429</v>
       </c>
       <c r="E3">
-        <v>-17.523</v>
+        <v>-11.946</v>
       </c>
       <c r="F3">
-        <v>5.577000000000001</v>
+        <v>11.154</v>
       </c>
       <c r="G3">
         <v>49.9</v>
@@ -1661,28 +1661,28 @@
         <v>24.1</v>
       </c>
       <c r="M3">
-        <v>0.2805231</v>
+        <v>0.5610462000000001</v>
       </c>
       <c r="N3">
-        <v>23.8194769</v>
+        <v>23.5389538</v>
       </c>
       <c r="O3">
         <v>0</v>
       </c>
       <c r="P3">
-        <v>23.8194769</v>
+        <v>23.5389538</v>
       </c>
       <c r="Q3">
-        <v>30.1194769</v>
+        <v>29.8389538</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1065621249895917</v>
+        <v>0.1071821466731589</v>
       </c>
       <c r="T3">
-        <v>1.184366912530911</v>
+        <v>1.196452289189389</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1699,7 +1699,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>85.9109285474173</v>
+        <v>42.95546427370865</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1707,22 +1707,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1060445037396957</v>
+        <v>0.1060895037396957</v>
       </c>
       <c r="C4">
-        <v>551.1767703074429</v>
+        <v>545.2172927079689</v>
       </c>
       <c r="D4">
-        <v>512.4307703074429</v>
+        <v>512.0482927079689</v>
       </c>
       <c r="E4">
-        <v>-11.946</v>
+        <v>-6.369</v>
       </c>
       <c r="F4">
-        <v>11.154</v>
+        <v>16.731</v>
       </c>
       <c r="G4">
         <v>49.9</v>
@@ -1743,28 +1743,28 @@
         <v>24.1</v>
       </c>
       <c r="M4">
-        <v>0.5610462000000001</v>
+        <v>0.8415693000000001</v>
       </c>
       <c r="N4">
-        <v>23.5389538</v>
+        <v>23.2584307</v>
       </c>
       <c r="O4">
         <v>0</v>
       </c>
       <c r="P4">
-        <v>23.5389538</v>
+        <v>23.2584307</v>
       </c>
       <c r="Q4">
-        <v>29.8389538</v>
+        <v>29.5584307</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1071821466731589</v>
+        <v>0.1078149523089647</v>
       </c>
       <c r="T4">
-        <v>1.196452289189389</v>
+        <v>1.208786848871754</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>42.95546427370865</v>
+        <v>28.63697618247243</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1789,22 +1789,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1060895037396957</v>
+        <v>0.1061345037396958</v>
       </c>
       <c r="C5">
-        <v>545.2172927079689</v>
+        <v>539.2583856441223</v>
       </c>
       <c r="D5">
-        <v>512.0482927079689</v>
+        <v>511.6663856441223</v>
       </c>
       <c r="E5">
-        <v>-6.369</v>
+        <v>-0.791999999999998</v>
       </c>
       <c r="F5">
-        <v>16.731</v>
+        <v>22.308</v>
       </c>
       <c r="G5">
         <v>49.9</v>
@@ -1825,28 +1825,28 @@
         <v>24.1</v>
       </c>
       <c r="M5">
-        <v>0.8415693000000001</v>
+        <v>1.1220924</v>
       </c>
       <c r="N5">
-        <v>23.2584307</v>
+        <v>22.9779076</v>
       </c>
       <c r="O5">
         <v>0</v>
       </c>
       <c r="P5">
-        <v>23.2584307</v>
+        <v>22.9779076</v>
       </c>
       <c r="Q5">
-        <v>29.5584307</v>
+        <v>29.2779076</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1078149523089647</v>
+        <v>0.1084609413955164</v>
       </c>
       <c r="T5">
-        <v>1.208786848871754</v>
+        <v>1.221378378547502</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1863,7 +1863,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>28.63697618247243</v>
+        <v>21.47773213685432</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1871,22 +1871,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1061345037396958</v>
+        <v>0.1061795037396957</v>
       </c>
       <c r="C6">
-        <v>539.2583856441223</v>
+        <v>533.3000478402669</v>
       </c>
       <c r="D6">
-        <v>511.6663856441223</v>
+        <v>511.2850478402668</v>
       </c>
       <c r="E6">
-        <v>-0.791999999999998</v>
+        <v>4.785000000000004</v>
       </c>
       <c r="F6">
-        <v>22.308</v>
+        <v>27.88500000000001</v>
       </c>
       <c r="G6">
         <v>49.9</v>
@@ -1907,28 +1907,28 @@
         <v>24.1</v>
       </c>
       <c r="M6">
-        <v>1.1220924</v>
+        <v>1.4026155</v>
       </c>
       <c r="N6">
-        <v>22.9779076</v>
+        <v>22.6973845</v>
       </c>
       <c r="O6">
         <v>0</v>
       </c>
       <c r="P6">
-        <v>22.9779076</v>
+        <v>22.6973845</v>
       </c>
       <c r="Q6">
-        <v>29.2779076</v>
+        <v>28.9973845</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1084609413955164</v>
+        <v>0.1091205302523113</v>
       </c>
       <c r="T6">
-        <v>1.221378378547502</v>
+        <v>1.234234993058528</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1945,7 +1945,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>21.47773213685432</v>
+        <v>17.18218570948346</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1953,22 +1953,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1061795037396957</v>
+        <v>0.1062245037396958</v>
       </c>
       <c r="C7">
-        <v>533.3000478402669</v>
+        <v>527.3422780245654</v>
       </c>
       <c r="D7">
-        <v>511.2850478402668</v>
+        <v>510.9042780245654</v>
       </c>
       <c r="E7">
-        <v>4.785000000000004</v>
+        <v>10.362</v>
       </c>
       <c r="F7">
-        <v>27.88500000000001</v>
+        <v>33.462</v>
       </c>
       <c r="G7">
         <v>49.9</v>
@@ -1989,28 +1989,28 @@
         <v>24.1</v>
       </c>
       <c r="M7">
-        <v>1.4026155</v>
+        <v>1.6831386</v>
       </c>
       <c r="N7">
-        <v>22.6973845</v>
+        <v>22.4168614</v>
       </c>
       <c r="O7">
         <v>0</v>
       </c>
       <c r="P7">
-        <v>22.6973845</v>
+        <v>22.4168614</v>
       </c>
       <c r="Q7">
-        <v>28.9973845</v>
+        <v>28.7168614</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1091205302523113</v>
+        <v>0.10979415291457</v>
       </c>
       <c r="T7">
-        <v>1.234234993058528</v>
+        <v>1.24736515255915</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2027,7 +2027,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>17.18218570948346</v>
+        <v>14.31848809123622</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2035,22 +2035,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1062245037396957</v>
+        <v>0.1063745037396958</v>
       </c>
       <c r="C8">
-        <v>527.3422780245655</v>
+        <v>520.5001311893059</v>
       </c>
       <c r="D8">
-        <v>510.9042780245655</v>
+        <v>509.6391311893058</v>
       </c>
       <c r="E8">
-        <v>10.362</v>
+        <v>15.939</v>
       </c>
       <c r="F8">
-        <v>33.462</v>
+        <v>39.039</v>
       </c>
       <c r="G8">
         <v>49.9</v>
@@ -2071,45 +2071,45 @@
         <v>24.1</v>
       </c>
       <c r="M8">
-        <v>1.6831386</v>
+        <v>2.0222202</v>
       </c>
       <c r="N8">
-        <v>22.4168614</v>
+        <v>22.0777798</v>
       </c>
       <c r="O8">
         <v>0</v>
       </c>
       <c r="P8">
-        <v>22.4168614</v>
+        <v>22.0777798</v>
       </c>
       <c r="Q8">
-        <v>28.7168614</v>
+        <v>28.3777798</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.10979415291457</v>
+        <v>0.1104822620856944</v>
       </c>
       <c r="T8">
-        <v>1.24736515255915</v>
+        <v>1.260777681081292</v>
       </c>
       <c r="U8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V8">
         <v>0</v>
       </c>
       <c r="W8">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y8">
-        <v>14.31848809123622</v>
+        <v>11.91759433517675</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -2117,22 +2117,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1063745037396958</v>
+        <v>0.1064345037396957</v>
       </c>
       <c r="C9">
-        <v>520.500131189306</v>
+        <v>514.418825126167</v>
       </c>
       <c r="D9">
-        <v>509.6391311893059</v>
+        <v>509.134825126167</v>
       </c>
       <c r="E9">
-        <v>15.93900000000001</v>
+        <v>21.51600000000001</v>
       </c>
       <c r="F9">
-        <v>39.03900000000001</v>
+        <v>44.61600000000001</v>
       </c>
       <c r="G9">
         <v>49.9</v>
@@ -2153,28 +2153,28 @@
         <v>24.1</v>
       </c>
       <c r="M9">
-        <v>2.0222202</v>
+        <v>2.3111088</v>
       </c>
       <c r="N9">
-        <v>22.0777798</v>
+        <v>21.7888912</v>
       </c>
       <c r="O9">
         <v>0</v>
       </c>
       <c r="P9">
-        <v>22.0777798</v>
+        <v>21.7888912</v>
       </c>
       <c r="Q9">
-        <v>28.3777798</v>
+        <v>28.0888912</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1104822620856944</v>
+        <v>0.1111853301518432</v>
       </c>
       <c r="T9">
-        <v>1.260777681081292</v>
+        <v>1.274481786310436</v>
       </c>
       <c r="U9">
         <v>0.0518</v>
@@ -2191,7 +2191,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>11.91759433517675</v>
+        <v>10.42789504327966</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2199,22 +2199,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1064345037396957</v>
+        <v>0.1066475037396958</v>
       </c>
       <c r="C10">
-        <v>514.418825126167</v>
+        <v>507.0595709483159</v>
       </c>
       <c r="D10">
-        <v>509.134825126167</v>
+        <v>507.3525709483159</v>
       </c>
       <c r="E10">
-        <v>21.51600000000001</v>
+        <v>27.093</v>
       </c>
       <c r="F10">
-        <v>44.61600000000001</v>
+        <v>50.193</v>
       </c>
       <c r="G10">
         <v>49.9</v>
@@ -2235,45 +2235,45 @@
         <v>24.1</v>
       </c>
       <c r="M10">
-        <v>2.3111088</v>
+        <v>2.6853255</v>
       </c>
       <c r="N10">
-        <v>21.7888912</v>
+        <v>21.4146745</v>
       </c>
       <c r="O10">
         <v>0</v>
       </c>
       <c r="P10">
-        <v>21.7888912</v>
+        <v>21.4146745</v>
       </c>
       <c r="Q10">
-        <v>28.0888912</v>
+        <v>27.7146745</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1111853301518432</v>
+        <v>0.1119038502634019</v>
       </c>
       <c r="T10">
-        <v>1.274481786310436</v>
+        <v>1.288487080665496</v>
       </c>
       <c r="U10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V10">
         <v>0</v>
       </c>
       <c r="W10">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y10">
-        <v>10.42789504327966</v>
+        <v>8.97470343911753</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2281,22 +2281,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1066475037396958</v>
+        <v>0.1067245037396958</v>
       </c>
       <c r="C11">
-        <v>507.0595709483159</v>
+        <v>500.8413486885511</v>
       </c>
       <c r="D11">
-        <v>507.3525709483159</v>
+        <v>506.7113486885511</v>
       </c>
       <c r="E11">
-        <v>27.093</v>
+        <v>32.67</v>
       </c>
       <c r="F11">
-        <v>50.193</v>
+        <v>55.77</v>
       </c>
       <c r="G11">
         <v>49.9</v>
@@ -2317,28 +2317,28 @@
         <v>24.1</v>
       </c>
       <c r="M11">
-        <v>2.6853255</v>
+        <v>2.983695</v>
       </c>
       <c r="N11">
-        <v>21.4146745</v>
+        <v>21.116305</v>
       </c>
       <c r="O11">
         <v>0</v>
       </c>
       <c r="P11">
-        <v>21.4146745</v>
+        <v>21.116305</v>
       </c>
       <c r="Q11">
-        <v>27.7146745</v>
+        <v>27.416305</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.1119038502634019</v>
+        <v>0.1126383374885508</v>
       </c>
       <c r="T11">
-        <v>1.288487080665496</v>
+        <v>1.302803603784002</v>
       </c>
       <c r="U11">
         <v>0.0535</v>
@@ -2355,7 +2355,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>8.97470343911753</v>
+        <v>8.077233095205777</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2363,22 +2363,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1067245037396958</v>
+        <v>0.1068895037396958</v>
       </c>
       <c r="C12">
-        <v>500.841348688551</v>
+        <v>493.8957441425089</v>
       </c>
       <c r="D12">
-        <v>506.711348688551</v>
+        <v>505.3427441425089</v>
       </c>
       <c r="E12">
-        <v>32.67000000000001</v>
+        <v>38.24700000000001</v>
       </c>
       <c r="F12">
-        <v>55.77000000000001</v>
+        <v>61.34700000000001</v>
       </c>
       <c r="G12">
         <v>49.9</v>
@@ -2399,45 +2399,45 @@
         <v>24.1</v>
       </c>
       <c r="M12">
-        <v>2.983695</v>
+        <v>3.331142100000001</v>
       </c>
       <c r="N12">
-        <v>21.116305</v>
+        <v>20.7688579</v>
       </c>
       <c r="O12">
         <v>0</v>
       </c>
       <c r="P12">
-        <v>21.116305</v>
+        <v>20.7688579</v>
       </c>
       <c r="Q12">
-        <v>27.416305</v>
+        <v>27.0688579</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1126383374885508</v>
+        <v>0.113389330044602</v>
       </c>
       <c r="T12">
-        <v>1.302803603784002</v>
+        <v>1.317441846523148</v>
       </c>
       <c r="U12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V12">
         <v>0</v>
       </c>
       <c r="W12">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y12">
-        <v>8.077233095205777</v>
+        <v>7.234755911493537</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1068895037396958</v>
+        <v>0.1069745037396957</v>
       </c>
       <c r="C13">
-        <v>493.8957441425089</v>
+        <v>487.6165866973929</v>
       </c>
       <c r="D13">
-        <v>505.3427441425089</v>
+        <v>504.6405866973929</v>
       </c>
       <c r="E13">
-        <v>38.24700000000001</v>
+        <v>43.82400000000001</v>
       </c>
       <c r="F13">
-        <v>61.34700000000001</v>
+        <v>66.92400000000001</v>
       </c>
       <c r="G13">
         <v>49.9</v>
@@ -2481,28 +2481,28 @@
         <v>24.1</v>
       </c>
       <c r="M13">
-        <v>3.331142100000001</v>
+        <v>3.6339732</v>
       </c>
       <c r="N13">
-        <v>20.7688579</v>
+        <v>20.4660268</v>
       </c>
       <c r="O13">
         <v>0</v>
       </c>
       <c r="P13">
-        <v>20.7688579</v>
+        <v>20.4660268</v>
       </c>
       <c r="Q13">
-        <v>27.0688579</v>
+        <v>26.7660268</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.113389330044602</v>
+        <v>0.1141573906132906</v>
       </c>
       <c r="T13">
-        <v>1.317441846523148</v>
+        <v>1.332412776597274</v>
       </c>
       <c r="U13">
         <v>0.0543</v>
@@ -2519,7 +2519,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>7.234755911493537</v>
+        <v>6.631859585535744</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2527,22 +2527,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1069745037396957</v>
+        <v>0.1070595037396957</v>
       </c>
       <c r="C14">
-        <v>487.6165866973929</v>
+        <v>481.3393777950887</v>
       </c>
       <c r="D14">
-        <v>504.6405866973929</v>
+        <v>503.9403777950886</v>
       </c>
       <c r="E14">
-        <v>43.82400000000001</v>
+        <v>49.401</v>
       </c>
       <c r="F14">
-        <v>66.92400000000001</v>
+        <v>72.501</v>
       </c>
       <c r="G14">
         <v>49.9</v>
@@ -2563,28 +2563,28 @@
         <v>24.1</v>
       </c>
       <c r="M14">
-        <v>3.6339732</v>
+        <v>3.9368043</v>
       </c>
       <c r="N14">
-        <v>20.4660268</v>
+        <v>20.1631957</v>
       </c>
       <c r="O14">
         <v>0</v>
       </c>
       <c r="P14">
-        <v>20.4660268</v>
+        <v>20.1631957</v>
       </c>
       <c r="Q14">
-        <v>26.7660268</v>
+        <v>26.4631957</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1141573906132906</v>
+        <v>0.1149431077467767</v>
       </c>
       <c r="T14">
-        <v>1.332412776597274</v>
+        <v>1.34772786598345</v>
       </c>
       <c r="U14">
         <v>0.0543</v>
@@ -2601,7 +2601,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>6.631859585535744</v>
+        <v>6.121716540494533</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2609,22 +2609,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1070595037396957</v>
+        <v>0.1072845037396958</v>
       </c>
       <c r="C15">
-        <v>481.3393777950887</v>
+        <v>473.9182288127052</v>
       </c>
       <c r="D15">
-        <v>503.9403777950886</v>
+        <v>502.0962288127052</v>
       </c>
       <c r="E15">
-        <v>49.401</v>
+        <v>54.97800000000002</v>
       </c>
       <c r="F15">
-        <v>72.501</v>
+        <v>78.07800000000002</v>
       </c>
       <c r="G15">
         <v>49.9</v>
@@ -2645,45 +2645,45 @@
         <v>24.1</v>
       </c>
       <c r="M15">
-        <v>3.9368043</v>
+        <v>4.317713400000001</v>
       </c>
       <c r="N15">
-        <v>20.1631957</v>
+        <v>19.7822866</v>
       </c>
       <c r="O15">
         <v>0</v>
       </c>
       <c r="P15">
-        <v>20.1631957</v>
+        <v>19.7822866</v>
       </c>
       <c r="Q15">
-        <v>26.4631957</v>
+        <v>26.0822866</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1149431077467767</v>
+        <v>0.1157470973717393</v>
       </c>
       <c r="T15">
-        <v>1.34772786598345</v>
+        <v>1.363399120239072</v>
       </c>
       <c r="U15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V15">
         <v>0</v>
       </c>
       <c r="W15">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y15">
-        <v>6.121716540494533</v>
+        <v>5.581658106348604</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2691,22 +2691,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1072845037396958</v>
+        <v>0.1073795037396958</v>
       </c>
       <c r="C16">
-        <v>473.9182288127052</v>
+        <v>467.5666343642205</v>
       </c>
       <c r="D16">
-        <v>502.0962288127052</v>
+        <v>501.3216343642205</v>
       </c>
       <c r="E16">
-        <v>54.97800000000002</v>
+        <v>60.55500000000001</v>
       </c>
       <c r="F16">
-        <v>78.07800000000002</v>
+        <v>83.65500000000002</v>
       </c>
       <c r="G16">
         <v>49.9</v>
@@ -2727,28 +2727,28 @@
         <v>24.1</v>
       </c>
       <c r="M16">
-        <v>4.317713400000001</v>
+        <v>4.626121500000001</v>
       </c>
       <c r="N16">
-        <v>19.7822866</v>
+        <v>19.4738785</v>
       </c>
       <c r="O16">
         <v>0</v>
       </c>
       <c r="P16">
-        <v>19.7822866</v>
+        <v>19.4738785</v>
       </c>
       <c r="Q16">
-        <v>26.0822866</v>
+        <v>25.7738785</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1157470973717393</v>
+        <v>0.1165700043996421</v>
       </c>
       <c r="T16">
-        <v>1.363399120239072</v>
+        <v>1.379439109888943</v>
       </c>
       <c r="U16">
         <v>0.0553</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>5.581658106348604</v>
+        <v>5.209547565925365</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2773,22 +2773,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1073795037396958</v>
+        <v>0.1074745037396957</v>
       </c>
       <c r="C17">
-        <v>467.5666343642206</v>
+        <v>461.2174262007694</v>
       </c>
       <c r="D17">
-        <v>501.3216343642205</v>
+        <v>500.5494262007694</v>
       </c>
       <c r="E17">
-        <v>60.555</v>
+        <v>66.13200000000001</v>
       </c>
       <c r="F17">
-        <v>83.655</v>
+        <v>89.23200000000001</v>
       </c>
       <c r="G17">
         <v>49.9</v>
@@ -2809,28 +2809,28 @@
         <v>24.1</v>
       </c>
       <c r="M17">
-        <v>4.6261215</v>
+        <v>4.934529600000001</v>
       </c>
       <c r="N17">
-        <v>19.4738785</v>
+        <v>19.1654704</v>
       </c>
       <c r="O17">
         <v>0</v>
       </c>
       <c r="P17">
-        <v>19.4738785</v>
+        <v>19.1654704</v>
       </c>
       <c r="Q17">
-        <v>25.7738785</v>
+        <v>25.4654704</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1165700043996421</v>
+        <v>0.1174125044520188</v>
       </c>
       <c r="T17">
-        <v>1.379439109888943</v>
+        <v>1.395861004054287</v>
       </c>
       <c r="U17">
         <v>0.0553</v>
@@ -2847,7 +2847,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>5.209547565925366</v>
+        <v>4.883950843055029</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2855,22 +2855,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1074745037396957</v>
+        <v>0.1075695037396958</v>
       </c>
       <c r="C18">
-        <v>461.2174262007694</v>
+        <v>454.8705933122056</v>
       </c>
       <c r="D18">
-        <v>500.5494262007694</v>
+        <v>499.7795933122056</v>
       </c>
       <c r="E18">
-        <v>66.13200000000001</v>
+        <v>71.709</v>
       </c>
       <c r="F18">
-        <v>89.23200000000001</v>
+        <v>94.80900000000001</v>
       </c>
       <c r="G18">
         <v>49.9</v>
@@ -2891,28 +2891,28 @@
         <v>24.1</v>
       </c>
       <c r="M18">
-        <v>4.934529600000001</v>
+        <v>5.242937700000001</v>
       </c>
       <c r="N18">
-        <v>19.1654704</v>
+        <v>18.8570623</v>
       </c>
       <c r="O18">
         <v>0</v>
       </c>
       <c r="P18">
-        <v>19.1654704</v>
+        <v>18.8570623</v>
       </c>
       <c r="Q18">
-        <v>25.4654704</v>
+        <v>25.1570623</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1174125044520188</v>
+        <v>0.1182753057104768</v>
       </c>
       <c r="T18">
-        <v>1.395861004054287</v>
+        <v>1.412678606512773</v>
       </c>
       <c r="U18">
         <v>0.0553</v>
@@ -2929,7 +2929,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>4.883950843055029</v>
+        <v>4.596659616992969</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2937,22 +2937,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1075695037396958</v>
+        <v>0.1081145037396957</v>
       </c>
       <c r="C19">
-        <v>454.8705933122056</v>
+        <v>444.9225422404848</v>
       </c>
       <c r="D19">
-        <v>499.7795933122056</v>
+        <v>495.4085422404848</v>
       </c>
       <c r="E19">
-        <v>71.709</v>
+        <v>77.28600000000003</v>
       </c>
       <c r="F19">
-        <v>94.80900000000001</v>
+        <v>100.386</v>
       </c>
       <c r="G19">
         <v>49.9</v>
@@ -2973,45 +2973,45 @@
         <v>24.1</v>
       </c>
       <c r="M19">
-        <v>5.242937700000001</v>
+        <v>5.802310800000002</v>
       </c>
       <c r="N19">
-        <v>18.8570623</v>
+        <v>18.2976892</v>
       </c>
       <c r="O19">
         <v>0</v>
       </c>
       <c r="P19">
-        <v>18.8570623</v>
+        <v>18.2976892</v>
       </c>
       <c r="Q19">
-        <v>25.1570623</v>
+        <v>24.5976892</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1182753057104768</v>
+        <v>0.119159150902068</v>
       </c>
       <c r="T19">
-        <v>1.412678606512773</v>
+        <v>1.429906394397075</v>
       </c>
       <c r="U19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V19">
         <v>0</v>
       </c>
       <c r="W19">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y19">
-        <v>4.596659616992969</v>
+        <v>4.153517595093319</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3019,22 +3019,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1081145037396958</v>
+        <v>0.1088995037396958</v>
       </c>
       <c r="C20">
-        <v>444.9225422404847</v>
+        <v>433.1823288614526</v>
       </c>
       <c r="D20">
-        <v>495.4085422404847</v>
+        <v>489.2453288614527</v>
       </c>
       <c r="E20">
-        <v>77.286</v>
+        <v>82.863</v>
       </c>
       <c r="F20">
-        <v>100.386</v>
+        <v>105.963</v>
       </c>
       <c r="G20">
         <v>49.9</v>
@@ -3055,45 +3055,45 @@
         <v>24.1</v>
       </c>
       <c r="M20">
-        <v>5.802310800000001</v>
+        <v>6.4955319</v>
       </c>
       <c r="N20">
-        <v>18.2976892</v>
+        <v>17.6044681</v>
       </c>
       <c r="O20">
         <v>0</v>
       </c>
       <c r="P20">
-        <v>18.2976892</v>
+        <v>17.6044681</v>
       </c>
       <c r="Q20">
-        <v>24.5976892</v>
+        <v>23.9044681</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.119159150902068</v>
+        <v>0.1200648194317231</v>
       </c>
       <c r="T20">
-        <v>1.429906394397075</v>
+        <v>1.447559559760002</v>
       </c>
       <c r="U20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V20">
         <v>0</v>
       </c>
       <c r="W20">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y20">
-        <v>4.15351759509332</v>
+        <v>3.710242728543909</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -3101,22 +3101,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1088995037396958</v>
+        <v>0.1090545037396958</v>
       </c>
       <c r="C21">
-        <v>433.1823288614526</v>
+        <v>426.40647310431</v>
       </c>
       <c r="D21">
-        <v>489.2453288614527</v>
+        <v>488.0464731043101</v>
       </c>
       <c r="E21">
-        <v>82.863</v>
+        <v>88.44000000000003</v>
       </c>
       <c r="F21">
-        <v>105.963</v>
+        <v>111.54</v>
       </c>
       <c r="G21">
         <v>49.9</v>
@@ -3137,28 +3137,28 @@
         <v>24.1</v>
       </c>
       <c r="M21">
-        <v>6.4955319</v>
+        <v>6.837402000000001</v>
       </c>
       <c r="N21">
-        <v>17.6044681</v>
+        <v>17.262598</v>
       </c>
       <c r="O21">
         <v>0</v>
       </c>
       <c r="P21">
-        <v>17.6044681</v>
+        <v>17.262598</v>
       </c>
       <c r="Q21">
-        <v>23.9044681</v>
+        <v>23.562598</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1200648194317231</v>
+        <v>0.1209931296746197</v>
       </c>
       <c r="T21">
-        <v>1.447559559760002</v>
+        <v>1.465654054257002</v>
       </c>
       <c r="U21">
         <v>0.0613</v>
@@ -3175,7 +3175,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>3.710242728543909</v>
+        <v>3.524730592116713</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3183,22 +3183,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1090545037396958</v>
+        <v>0.1097975037396958</v>
       </c>
       <c r="C22">
-        <v>426.40647310431</v>
+        <v>415.1633375782836</v>
       </c>
       <c r="D22">
-        <v>488.0464731043101</v>
+        <v>482.3803375782836</v>
       </c>
       <c r="E22">
-        <v>88.44000000000003</v>
+        <v>94.01700000000002</v>
       </c>
       <c r="F22">
-        <v>111.54</v>
+        <v>117.117</v>
       </c>
       <c r="G22">
         <v>49.9</v>
@@ -3219,45 +3219,45 @@
         <v>24.1</v>
       </c>
       <c r="M22">
-        <v>6.837402000000001</v>
+        <v>7.507199700000002</v>
       </c>
       <c r="N22">
-        <v>17.262598</v>
+        <v>16.5928003</v>
       </c>
       <c r="O22">
         <v>0</v>
       </c>
       <c r="P22">
-        <v>17.262598</v>
+        <v>16.5928003</v>
       </c>
       <c r="Q22">
-        <v>23.562598</v>
+        <v>22.8928003</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1209931296746197</v>
+        <v>0.1219449414426529</v>
       </c>
       <c r="T22">
-        <v>1.465654054257002</v>
+        <v>1.48420663722228</v>
       </c>
       <c r="U22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V22">
         <v>0</v>
       </c>
       <c r="W22">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y22">
-        <v>3.524730592116713</v>
+        <v>3.210251620188017</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3265,22 +3265,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1097975037396958</v>
+        <v>0.1099805037396958</v>
       </c>
       <c r="C23">
-        <v>415.1633375782836</v>
+        <v>408.2109105150301</v>
       </c>
       <c r="D23">
-        <v>482.3803375782836</v>
+        <v>481.0049105150301</v>
       </c>
       <c r="E23">
-        <v>94.017</v>
+        <v>99.59400000000002</v>
       </c>
       <c r="F23">
-        <v>117.117</v>
+        <v>122.694</v>
       </c>
       <c r="G23">
         <v>49.9</v>
@@ -3301,28 +3301,28 @@
         <v>24.1</v>
       </c>
       <c r="M23">
-        <v>7.507199700000001</v>
+        <v>7.864685400000002</v>
       </c>
       <c r="N23">
-        <v>16.5928003</v>
+        <v>16.2353146</v>
       </c>
       <c r="O23">
         <v>0</v>
       </c>
       <c r="P23">
-        <v>16.5928003</v>
+        <v>16.2353146</v>
       </c>
       <c r="Q23">
-        <v>22.8928003</v>
+        <v>22.5353146</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1219449414426529</v>
+        <v>0.1229211586406356</v>
       </c>
       <c r="T23">
-        <v>1.48420663722228</v>
+        <v>1.503234927443079</v>
       </c>
       <c r="U23">
         <v>0.0641</v>
@@ -3339,7 +3339,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>3.210251620188017</v>
+        <v>3.064331091997653</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3347,22 +3347,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1099805037396958</v>
+        <v>0.1119575037396958</v>
       </c>
       <c r="C24">
-        <v>408.2109105150301</v>
+        <v>388.2599294194037</v>
       </c>
       <c r="D24">
-        <v>481.0049105150301</v>
+        <v>466.6309294194037</v>
       </c>
       <c r="E24">
-        <v>99.59400000000002</v>
+        <v>105.171</v>
       </c>
       <c r="F24">
-        <v>122.694</v>
+        <v>128.271</v>
       </c>
       <c r="G24">
         <v>49.9</v>
@@ -3383,45 +3383,45 @@
         <v>24.1</v>
       </c>
       <c r="M24">
-        <v>7.864685400000002</v>
+        <v>9.222684900000003</v>
       </c>
       <c r="N24">
-        <v>16.2353146</v>
+        <v>14.8773151</v>
       </c>
       <c r="O24">
         <v>0</v>
       </c>
       <c r="P24">
-        <v>16.2353146</v>
+        <v>14.8773151</v>
       </c>
       <c r="Q24">
-        <v>22.5353146</v>
+        <v>21.17731509999999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1229211586406356</v>
+        <v>0.123922732129475</v>
       </c>
       <c r="T24">
-        <v>1.503234927443079</v>
+        <v>1.522757458968313</v>
       </c>
       <c r="U24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V24">
         <v>0</v>
       </c>
       <c r="W24">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y24">
-        <v>3.064331091997653</v>
+        <v>2.613121912036699</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3429,22 +3429,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1119575037396958</v>
+        <v>0.1122185037396958</v>
       </c>
       <c r="C25">
-        <v>388.2599294194037</v>
+        <v>380.8492435378942</v>
       </c>
       <c r="D25">
-        <v>466.6309294194037</v>
+        <v>464.7972435378942</v>
       </c>
       <c r="E25">
-        <v>105.171</v>
+        <v>110.748</v>
       </c>
       <c r="F25">
-        <v>128.271</v>
+        <v>133.848</v>
       </c>
       <c r="G25">
         <v>49.9</v>
@@ -3465,28 +3465,28 @@
         <v>24.1</v>
       </c>
       <c r="M25">
-        <v>9.222684900000003</v>
+        <v>9.623671200000002</v>
       </c>
       <c r="N25">
-        <v>14.8773151</v>
+        <v>14.4763288</v>
       </c>
       <c r="O25">
         <v>0</v>
       </c>
       <c r="P25">
-        <v>14.8773151</v>
+        <v>14.4763288</v>
       </c>
       <c r="Q25">
-        <v>21.17731509999999</v>
+        <v>20.77632879999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.123922732129475</v>
+        <v>0.1249506628153892</v>
       </c>
       <c r="T25">
-        <v>1.522757458968313</v>
+        <v>1.54279374132316</v>
       </c>
       <c r="U25">
         <v>0.07190000000000001</v>
@@ -3503,7 +3503,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>2.613121912036699</v>
+        <v>2.504241832368503</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1122185037396958</v>
+        <v>0.1134545037396957</v>
       </c>
       <c r="C26">
-        <v>380.8492435378942</v>
+        <v>366.7807261775245</v>
       </c>
       <c r="D26">
-        <v>464.7972435378942</v>
+        <v>456.3057261775245</v>
       </c>
       <c r="E26">
-        <v>110.748</v>
+        <v>116.325</v>
       </c>
       <c r="F26">
-        <v>133.848</v>
+        <v>139.425</v>
       </c>
       <c r="G26">
         <v>49.9</v>
@@ -3547,45 +3547,45 @@
         <v>24.1</v>
       </c>
       <c r="M26">
-        <v>9.623671200000002</v>
+        <v>10.568415</v>
       </c>
       <c r="N26">
-        <v>14.4763288</v>
+        <v>13.531585</v>
       </c>
       <c r="O26">
         <v>0</v>
       </c>
       <c r="P26">
-        <v>14.4763288</v>
+        <v>13.531585</v>
       </c>
       <c r="Q26">
-        <v>20.77632879999999</v>
+        <v>19.831585</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1249506628153892</v>
+        <v>0.126006004986261</v>
       </c>
       <c r="T26">
-        <v>1.54279374132316</v>
+        <v>1.563364324540802</v>
       </c>
       <c r="U26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V26">
         <v>0</v>
       </c>
       <c r="W26">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y26">
-        <v>2.504241832368503</v>
+        <v>2.280379792050179</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3593,22 +3593,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1134545037396957</v>
+        <v>0.1137545037396957</v>
       </c>
       <c r="C27">
-        <v>366.7807261775245</v>
+        <v>359.1892648788645</v>
       </c>
       <c r="D27">
-        <v>456.3057261775245</v>
+        <v>454.2912648788646</v>
       </c>
       <c r="E27">
-        <v>116.325</v>
+        <v>121.902</v>
       </c>
       <c r="F27">
-        <v>139.425</v>
+        <v>145.002</v>
       </c>
       <c r="G27">
         <v>49.9</v>
@@ -3629,28 +3629,28 @@
         <v>24.1</v>
       </c>
       <c r="M27">
-        <v>10.568415</v>
+        <v>10.9911516</v>
       </c>
       <c r="N27">
-        <v>13.531585</v>
+        <v>13.1088484</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>13.531585</v>
+        <v>13.1088484</v>
       </c>
       <c r="Q27">
-        <v>19.831585</v>
+        <v>19.4088484</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.126006004986261</v>
+        <v>0.1270898699185078</v>
       </c>
       <c r="T27">
-        <v>1.563364324540802</v>
+        <v>1.584490869467029</v>
       </c>
       <c r="U27">
         <v>0.07580000000000001</v>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>2.280379792050179</v>
+        <v>2.192672876971327</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3675,22 +3675,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1137545037396957</v>
+        <v>0.1140545037396958</v>
       </c>
       <c r="C28">
-        <v>359.1892648788645</v>
+        <v>351.6155119615269</v>
       </c>
       <c r="D28">
-        <v>454.2912648788646</v>
+        <v>452.294511961527</v>
       </c>
       <c r="E28">
-        <v>121.902</v>
+        <v>127.479</v>
       </c>
       <c r="F28">
-        <v>145.002</v>
+        <v>150.579</v>
       </c>
       <c r="G28">
         <v>49.9</v>
@@ -3711,28 +3711,28 @@
         <v>24.1</v>
       </c>
       <c r="M28">
-        <v>10.9911516</v>
+        <v>11.4138882</v>
       </c>
       <c r="N28">
-        <v>13.1088484</v>
+        <v>12.6861118</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>13.1088484</v>
+        <v>12.6861118</v>
       </c>
       <c r="Q28">
-        <v>19.4088484</v>
+        <v>18.9861118</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1270898699185078</v>
+        <v>0.1282034297804052</v>
       </c>
       <c r="T28">
-        <v>1.584490869467029</v>
+        <v>1.60619622384329</v>
       </c>
       <c r="U28">
         <v>0.07580000000000001</v>
@@ -3749,7 +3749,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>2.192672876971327</v>
+        <v>2.111462770416833</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3757,22 +3757,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1140545037396958</v>
+        <v>0.1143545037396958</v>
       </c>
       <c r="C29">
-        <v>351.6155119615269</v>
+        <v>344.0592349456263</v>
       </c>
       <c r="D29">
-        <v>452.294511961527</v>
+        <v>450.3152349456263</v>
       </c>
       <c r="E29">
-        <v>127.479</v>
+        <v>133.056</v>
       </c>
       <c r="F29">
-        <v>150.579</v>
+        <v>156.156</v>
       </c>
       <c r="G29">
         <v>49.9</v>
@@ -3793,28 +3793,28 @@
         <v>24.1</v>
       </c>
       <c r="M29">
-        <v>11.4138882</v>
+        <v>11.8366248</v>
       </c>
       <c r="N29">
-        <v>12.6861118</v>
+        <v>12.2633752</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>12.6861118</v>
+        <v>12.2633752</v>
       </c>
       <c r="Q29">
-        <v>18.9861118</v>
+        <v>18.5633752</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1282034297804052</v>
+        <v>0.1293479218606886</v>
       </c>
       <c r="T29">
-        <v>1.60619622384329</v>
+        <v>1.628504504730002</v>
       </c>
       <c r="U29">
         <v>0.07580000000000001</v>
@@ -3831,7 +3831,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>2.111462770416833</v>
+        <v>2.036053385759089</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3839,22 +3839,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1143545037396958</v>
+        <v>0.1187725037396958</v>
       </c>
       <c r="C30">
-        <v>344.0592349456263</v>
+        <v>311.2186410433723</v>
       </c>
       <c r="D30">
-        <v>450.3152349456263</v>
+        <v>423.0516410433723</v>
       </c>
       <c r="E30">
-        <v>133.056</v>
+        <v>138.633</v>
       </c>
       <c r="F30">
-        <v>156.156</v>
+        <v>161.733</v>
       </c>
       <c r="G30">
         <v>49.9</v>
@@ -3875,45 +3875,45 @@
         <v>24.1</v>
       </c>
       <c r="M30">
-        <v>11.8366248</v>
+        <v>14.55597</v>
       </c>
       <c r="N30">
-        <v>12.2633752</v>
+        <v>9.544029999999999</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>12.2633752</v>
+        <v>9.544029999999999</v>
       </c>
       <c r="Q30">
-        <v>18.5633752</v>
+        <v>15.84403</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1293479218606886</v>
+        <v>0.1305246531545011</v>
       </c>
       <c r="T30">
-        <v>1.628504504730002</v>
+        <v>1.651441187895213</v>
       </c>
       <c r="U30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V30">
         <v>0</v>
       </c>
       <c r="W30">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y30">
-        <v>2.036053385759089</v>
+        <v>1.655678048250993</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3921,22 +3921,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1187725037396957</v>
+        <v>0.1192145037396957</v>
       </c>
       <c r="C31">
-        <v>311.2186410433724</v>
+        <v>303.0946126523045</v>
       </c>
       <c r="D31">
-        <v>423.0516410433724</v>
+        <v>420.5046126523045</v>
       </c>
       <c r="E31">
-        <v>138.633</v>
+        <v>144.21</v>
       </c>
       <c r="F31">
-        <v>161.733</v>
+        <v>167.31</v>
       </c>
       <c r="G31">
         <v>49.9</v>
@@ -3957,28 +3957,28 @@
         <v>24.1</v>
       </c>
       <c r="M31">
-        <v>14.55597</v>
+        <v>15.0579</v>
       </c>
       <c r="N31">
-        <v>9.544030000000001</v>
+        <v>9.042100000000001</v>
       </c>
       <c r="O31">
         <v>0</v>
       </c>
       <c r="P31">
-        <v>9.544030000000001</v>
+        <v>9.042100000000001</v>
       </c>
       <c r="Q31">
-        <v>15.84403</v>
+        <v>15.3421</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.130524653154501</v>
+        <v>0.1317350053424225</v>
       </c>
       <c r="T31">
-        <v>1.651441187895213</v>
+        <v>1.675033204865145</v>
       </c>
       <c r="U31">
         <v>0.09</v>
@@ -3995,7 +3995,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>1.655678048250993</v>
+        <v>1.60048877997596</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4003,22 +4003,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1192145037396957</v>
+        <v>0.1196565037396957</v>
       </c>
       <c r="C32">
-        <v>303.0946126523045</v>
+        <v>295.0010700408727</v>
       </c>
       <c r="D32">
-        <v>420.5046126523045</v>
+        <v>417.9880700408727</v>
       </c>
       <c r="E32">
-        <v>144.21</v>
+        <v>149.787</v>
       </c>
       <c r="F32">
-        <v>167.31</v>
+        <v>172.887</v>
       </c>
       <c r="G32">
         <v>49.9</v>
@@ -4039,28 +4039,28 @@
         <v>24.1</v>
       </c>
       <c r="M32">
-        <v>15.0579</v>
+        <v>15.55983</v>
       </c>
       <c r="N32">
-        <v>9.042100000000001</v>
+        <v>8.540170000000002</v>
       </c>
       <c r="O32">
         <v>0</v>
       </c>
       <c r="P32">
-        <v>9.042100000000001</v>
+        <v>8.540170000000002</v>
       </c>
       <c r="Q32">
-        <v>15.3421</v>
+        <v>14.84017</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1317350053424225</v>
+        <v>0.1329804402024576</v>
       </c>
       <c r="T32">
-        <v>1.675033204865145</v>
+        <v>1.699309048413915</v>
       </c>
       <c r="U32">
         <v>0.09</v>
@@ -4077,7 +4077,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>1.60048877997596</v>
+        <v>1.548860109654155</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -4085,22 +4085,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1196565037396957</v>
+        <v>0.1200985037396957</v>
       </c>
       <c r="C33">
-        <v>295.0010700408727</v>
+        <v>286.9374691315818</v>
       </c>
       <c r="D33">
-        <v>417.9880700408727</v>
+        <v>415.5014691315819</v>
       </c>
       <c r="E33">
-        <v>149.787</v>
+        <v>155.364</v>
       </c>
       <c r="F33">
-        <v>172.887</v>
+        <v>178.464</v>
       </c>
       <c r="G33">
         <v>49.9</v>
@@ -4121,28 +4121,28 @@
         <v>24.1</v>
       </c>
       <c r="M33">
-        <v>15.55983</v>
+        <v>16.06176</v>
       </c>
       <c r="N33">
-        <v>8.540170000000002</v>
+        <v>8.038239999999998</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>8.540170000000002</v>
+        <v>8.038239999999998</v>
       </c>
       <c r="Q33">
-        <v>14.84017</v>
+        <v>14.33824</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1329804402024576</v>
+        <v>0.1342625054995526</v>
       </c>
       <c r="T33">
-        <v>1.699309048413915</v>
+        <v>1.724298887361179</v>
       </c>
       <c r="U33">
         <v>0.09</v>
@@ -4159,7 +4159,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>1.548860109654155</v>
+        <v>1.500458231227462</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4167,22 +4167,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1200985037396957</v>
+        <v>0.1392845037396958</v>
       </c>
       <c r="C34">
-        <v>286.9374691315818</v>
+        <v>196.0863234939716</v>
       </c>
       <c r="D34">
-        <v>415.5014691315819</v>
+        <v>330.2273234939717</v>
       </c>
       <c r="E34">
-        <v>155.364</v>
+        <v>160.941</v>
       </c>
       <c r="F34">
-        <v>178.464</v>
+        <v>184.041</v>
       </c>
       <c r="G34">
         <v>49.9</v>
@@ -4203,45 +4203,45 @@
         <v>24.1</v>
       </c>
       <c r="M34">
-        <v>16.06176</v>
+        <v>27.01721880000001</v>
       </c>
       <c r="N34">
-        <v>8.038239999999998</v>
+        <v>-2.917218800000004</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P34">
-        <v>8.038239999999998</v>
+        <v>-2.917218800000004</v>
       </c>
       <c r="Q34">
-        <v>14.33824</v>
+        <v>3.382781199999993</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1342625054995526</v>
+        <v>0.135582841402531</v>
       </c>
       <c r="T34">
-        <v>1.724298887361179</v>
+        <v>1.750034691650151</v>
       </c>
       <c r="U34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V34">
         <v>0</v>
       </c>
       <c r="W34">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y34">
-        <v>1.500458231227462</v>
+        <v>0.89202371933265</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4249,22 +4249,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1392845037396958</v>
+        <v>0.1402945037396957</v>
       </c>
       <c r="C35">
-        <v>196.0863234939716</v>
+        <v>186.9797044840905</v>
       </c>
       <c r="D35">
-        <v>330.2273234939717</v>
+        <v>326.6977044840906</v>
       </c>
       <c r="E35">
-        <v>160.941</v>
+        <v>166.518</v>
       </c>
       <c r="F35">
-        <v>184.041</v>
+        <v>189.618</v>
       </c>
       <c r="G35">
         <v>49.9</v>
@@ -4285,28 +4285,28 @@
         <v>24.1</v>
       </c>
       <c r="M35">
-        <v>27.01721880000001</v>
+        <v>27.8359224</v>
       </c>
       <c r="N35">
-        <v>-2.917218800000004</v>
+        <v>-3.735922400000003</v>
       </c>
       <c r="O35">
         <v>-0</v>
       </c>
       <c r="P35">
-        <v>-2.917218800000004</v>
+        <v>-3.735922400000003</v>
       </c>
       <c r="Q35">
-        <v>3.382781199999993</v>
+        <v>2.564077599999994</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.135582841402531</v>
+        <v>0.1369431874843875</v>
       </c>
       <c r="T35">
-        <v>1.750034691650151</v>
+        <v>1.776550368796366</v>
       </c>
       <c r="U35">
         <v>0.1468</v>
@@ -4323,7 +4323,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>0.89202371933265</v>
+        <v>0.8657877275875722</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4331,22 +4331,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1402945037396957</v>
+        <v>0.1413045037396957</v>
       </c>
       <c r="C36">
-        <v>186.9797044840905</v>
+        <v>177.9477398634872</v>
       </c>
       <c r="D36">
-        <v>326.6977044840906</v>
+        <v>323.2427398634872</v>
       </c>
       <c r="E36">
-        <v>166.518</v>
+        <v>172.095</v>
       </c>
       <c r="F36">
-        <v>189.618</v>
+        <v>195.195</v>
       </c>
       <c r="G36">
         <v>49.9</v>
@@ -4367,28 +4367,28 @@
         <v>24.1</v>
       </c>
       <c r="M36">
-        <v>27.8359224</v>
+        <v>28.65462600000001</v>
       </c>
       <c r="N36">
-        <v>-3.735922400000003</v>
+        <v>-4.554626000000006</v>
       </c>
       <c r="O36">
         <v>-0</v>
       </c>
       <c r="P36">
-        <v>-3.735922400000003</v>
+        <v>-4.554626000000006</v>
       </c>
       <c r="Q36">
-        <v>2.564077599999994</v>
+        <v>1.745373999999991</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1369431874843875</v>
+        <v>0.1383453903687627</v>
       </c>
       <c r="T36">
-        <v>1.776550368796366</v>
+        <v>1.803881912931695</v>
       </c>
       <c r="U36">
         <v>0.1468</v>
@@ -4405,7 +4405,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>0.8657877275875722</v>
+        <v>0.8410509353707842</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4413,22 +4413,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1413045037396957</v>
+        <v>0.1423145037396958</v>
       </c>
       <c r="C37">
-        <v>177.9477398634872</v>
+        <v>168.9880859139559</v>
       </c>
       <c r="D37">
-        <v>323.2427398634872</v>
+        <v>319.860085913956</v>
       </c>
       <c r="E37">
-        <v>172.095</v>
+        <v>177.6720000000001</v>
       </c>
       <c r="F37">
-        <v>195.195</v>
+        <v>200.772</v>
       </c>
       <c r="G37">
         <v>49.9</v>
@@ -4449,28 +4449,28 @@
         <v>24.1</v>
       </c>
       <c r="M37">
-        <v>28.65462600000001</v>
+        <v>29.47332960000001</v>
       </c>
       <c r="N37">
-        <v>-4.554626000000006</v>
+        <v>-5.373329600000009</v>
       </c>
       <c r="O37">
         <v>-0</v>
       </c>
       <c r="P37">
-        <v>-4.554626000000006</v>
+        <v>-5.373329600000009</v>
       </c>
       <c r="Q37">
-        <v>1.745373999999991</v>
+        <v>0.9266703999999883</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1383453903687627</v>
+        <v>0.1397914120932746</v>
       </c>
       <c r="T37">
-        <v>1.803881912931695</v>
+        <v>1.832067567821252</v>
       </c>
       <c r="U37">
         <v>0.1468</v>
@@ -4487,7 +4487,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>0.8410509353707842</v>
+        <v>0.8176884093882624</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4495,22 +4495,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1423145037396958</v>
+        <v>0.1633045037396958</v>
       </c>
       <c r="C38">
-        <v>168.9880859139559</v>
+        <v>106.2740146557601</v>
       </c>
       <c r="D38">
-        <v>319.860085913956</v>
+        <v>262.7230146557601</v>
       </c>
       <c r="E38">
-        <v>177.672</v>
+        <v>183.249</v>
       </c>
       <c r="F38">
-        <v>200.772</v>
+        <v>206.349</v>
       </c>
       <c r="G38">
         <v>49.9</v>
@@ -4531,45 +4531,45 @@
         <v>24.1</v>
       </c>
       <c r="M38">
-        <v>29.47332960000001</v>
+        <v>41.4348792</v>
       </c>
       <c r="N38">
-        <v>-5.373329600000005</v>
+        <v>-17.3348792</v>
       </c>
       <c r="O38">
         <v>-0</v>
       </c>
       <c r="P38">
-        <v>-5.373329600000005</v>
+        <v>-17.3348792</v>
       </c>
       <c r="Q38">
-        <v>0.9266703999999919</v>
+        <v>-11.03487920000001</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1397914120932746</v>
+        <v>0.1412833392693583</v>
       </c>
       <c r="T38">
-        <v>1.832067567821252</v>
+        <v>1.861148005405717</v>
       </c>
       <c r="U38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V38">
         <v>0</v>
       </c>
       <c r="W38">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y38">
-        <v>0.8176884093882626</v>
+        <v>0.5816355801032478</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1633045037396958</v>
+        <v>0.1648545037396957</v>
       </c>
       <c r="C39">
-        <v>106.2740146557601</v>
+        <v>97.27655881473802</v>
       </c>
       <c r="D39">
-        <v>262.7230146557601</v>
+        <v>259.3025588147381</v>
       </c>
       <c r="E39">
-        <v>183.249</v>
+        <v>188.826</v>
       </c>
       <c r="F39">
-        <v>206.349</v>
+        <v>211.926</v>
       </c>
       <c r="G39">
         <v>49.9</v>
@@ -4613,28 +4613,28 @@
         <v>24.1</v>
       </c>
       <c r="M39">
-        <v>41.4348792</v>
+        <v>42.5547408</v>
       </c>
       <c r="N39">
-        <v>-17.3348792</v>
+        <v>-18.4547408</v>
       </c>
       <c r="O39">
         <v>-0</v>
       </c>
       <c r="P39">
-        <v>-17.3348792</v>
+        <v>-18.4547408</v>
       </c>
       <c r="Q39">
-        <v>-11.03487920000001</v>
+        <v>-12.15474080000001</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1412833392693583</v>
+        <v>0.1428233931285415</v>
       </c>
       <c r="T39">
-        <v>1.861148005405717</v>
+        <v>1.891166521621938</v>
       </c>
       <c r="U39">
         <v>0.2008</v>
@@ -4651,7 +4651,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>0.5816355801032478</v>
+        <v>0.5663293806268466</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4659,22 +4659,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1648545037396957</v>
+        <v>0.1664045037396958</v>
       </c>
       <c r="C40">
-        <v>97.27655881473802</v>
+        <v>88.36702185550209</v>
       </c>
       <c r="D40">
-        <v>259.3025588147381</v>
+        <v>255.9700218555021</v>
       </c>
       <c r="E40">
-        <v>188.826</v>
+        <v>194.403</v>
       </c>
       <c r="F40">
-        <v>211.926</v>
+        <v>217.503</v>
       </c>
       <c r="G40">
         <v>49.9</v>
@@ -4695,28 +4695,28 @@
         <v>24.1</v>
       </c>
       <c r="M40">
-        <v>42.5547408</v>
+        <v>43.6746024</v>
       </c>
       <c r="N40">
-        <v>-18.4547408</v>
+        <v>-19.5746024</v>
       </c>
       <c r="O40">
         <v>-0</v>
       </c>
       <c r="P40">
-        <v>-18.4547408</v>
+        <v>-19.5746024</v>
       </c>
       <c r="Q40">
-        <v>-12.15474080000001</v>
+        <v>-13.27460240000001</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1428233931285415</v>
+        <v>0.1444139405568783</v>
       </c>
       <c r="T40">
-        <v>1.891166521621938</v>
+        <v>1.922169251484593</v>
       </c>
       <c r="U40">
         <v>0.2008</v>
@@ -4733,7 +4733,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>0.5663293806268466</v>
+        <v>0.5518081144569275</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4741,22 +4741,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1664045037396958</v>
+        <v>0.1679545037396958</v>
       </c>
       <c r="C41">
-        <v>88.36702185550209</v>
+        <v>79.5420570099202</v>
       </c>
       <c r="D41">
-        <v>255.9700218555021</v>
+        <v>252.7220570099203</v>
       </c>
       <c r="E41">
-        <v>194.403</v>
+        <v>199.98</v>
       </c>
       <c r="F41">
-        <v>217.503</v>
+        <v>223.08</v>
       </c>
       <c r="G41">
         <v>49.9</v>
@@ -4777,28 +4777,28 @@
         <v>24.1</v>
       </c>
       <c r="M41">
-        <v>43.6746024</v>
+        <v>44.79446400000001</v>
       </c>
       <c r="N41">
-        <v>-19.5746024</v>
+        <v>-20.69446400000001</v>
       </c>
       <c r="O41">
         <v>-0</v>
       </c>
       <c r="P41">
-        <v>-19.5746024</v>
+        <v>-20.69446400000001</v>
       </c>
       <c r="Q41">
-        <v>-13.27460240000001</v>
+        <v>-14.39446400000001</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1444139405568783</v>
+        <v>0.1460575062328263</v>
       </c>
       <c r="T41">
-        <v>1.922169251484593</v>
+        <v>1.954205405676003</v>
       </c>
       <c r="U41">
         <v>0.2008</v>
@@ -4815,7 +4815,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>0.5518081144569275</v>
+        <v>0.5380129115955041</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4823,22 +4823,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1679545037396958</v>
+        <v>0.1695045037396958</v>
       </c>
       <c r="C42">
-        <v>79.5420570099202</v>
+        <v>70.79848524799269</v>
       </c>
       <c r="D42">
-        <v>252.7220570099203</v>
+        <v>249.5554852479927</v>
       </c>
       <c r="E42">
-        <v>199.98</v>
+        <v>205.557</v>
       </c>
       <c r="F42">
-        <v>223.08</v>
+        <v>228.657</v>
       </c>
       <c r="G42">
         <v>49.9</v>
@@ -4859,28 +4859,28 @@
         <v>24.1</v>
       </c>
       <c r="M42">
-        <v>44.79446400000001</v>
+        <v>45.91432560000001</v>
       </c>
       <c r="N42">
-        <v>-20.69446400000001</v>
+        <v>-21.81432560000001</v>
       </c>
       <c r="O42">
         <v>-0</v>
       </c>
       <c r="P42">
-        <v>-20.69446400000001</v>
+        <v>-21.81432560000001</v>
       </c>
       <c r="Q42">
-        <v>-14.39446400000001</v>
+        <v>-15.51432560000001</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1460575062328263</v>
+        <v>0.1477567859994843</v>
       </c>
       <c r="T42">
-        <v>1.954205405676003</v>
+        <v>1.987327531195935</v>
       </c>
       <c r="U42">
         <v>0.2008</v>
@@ -4897,7 +4897,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>0.5380129115955041</v>
+        <v>0.5248906454590285</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4905,22 +4905,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1695045037396958</v>
+        <v>0.1710545037396957</v>
       </c>
       <c r="C43">
-        <v>70.79848524799269</v>
+        <v>62.13328489921918</v>
       </c>
       <c r="D43">
-        <v>249.5554852479927</v>
+        <v>246.4672848992192</v>
       </c>
       <c r="E43">
-        <v>205.557</v>
+        <v>211.134</v>
       </c>
       <c r="F43">
-        <v>228.657</v>
+        <v>234.234</v>
       </c>
       <c r="G43">
         <v>49.9</v>
@@ -4941,28 +4941,28 @@
         <v>24.1</v>
       </c>
       <c r="M43">
-        <v>45.91432560000001</v>
+        <v>47.03418720000001</v>
       </c>
       <c r="N43">
-        <v>-21.81432560000001</v>
+        <v>-22.93418720000001</v>
       </c>
       <c r="O43">
         <v>-0</v>
       </c>
       <c r="P43">
-        <v>-21.81432560000001</v>
+        <v>-22.93418720000001</v>
       </c>
       <c r="Q43">
-        <v>-15.51432560000001</v>
+        <v>-16.63418720000001</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1477567859994843</v>
+        <v>0.1495146616201651</v>
       </c>
       <c r="T43">
-        <v>1.987327531195935</v>
+        <v>2.021591798975175</v>
       </c>
       <c r="U43">
         <v>0.2008</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>0.5248906454590285</v>
+        <v>0.5123932491385754</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4987,22 +4987,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1710545037396957</v>
+        <v>0.1726045037396958</v>
       </c>
       <c r="C44">
-        <v>62.13328489921921</v>
+        <v>53.54358203514735</v>
       </c>
       <c r="D44">
-        <v>246.4672848992192</v>
+        <v>243.4545820351474</v>
       </c>
       <c r="E44">
-        <v>211.134</v>
+        <v>216.711</v>
       </c>
       <c r="F44">
-        <v>234.234</v>
+        <v>239.811</v>
       </c>
       <c r="G44">
         <v>49.9</v>
@@ -5023,28 +5023,28 @@
         <v>24.1</v>
       </c>
       <c r="M44">
-        <v>47.03418720000001</v>
+        <v>48.15404880000001</v>
       </c>
       <c r="N44">
-        <v>-22.9341872</v>
+        <v>-24.0540488</v>
       </c>
       <c r="O44">
         <v>-0</v>
       </c>
       <c r="P44">
-        <v>-22.9341872</v>
+        <v>-24.0540488</v>
       </c>
       <c r="Q44">
-        <v>-16.63418720000001</v>
+        <v>-17.75404880000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1495146616201651</v>
+        <v>0.1513342170871855</v>
       </c>
       <c r="T44">
-        <v>2.021591798975175</v>
+        <v>2.057058321764213</v>
       </c>
       <c r="U44">
         <v>0.2008</v>
@@ -5061,7 +5061,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>0.5123932491385754</v>
+        <v>0.5004771270655854</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -5069,22 +5069,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1726045037396958</v>
+        <v>0.1895545037396958</v>
       </c>
       <c r="C45">
-        <v>53.54358203514735</v>
+        <v>19.26101067462889</v>
       </c>
       <c r="D45">
-        <v>243.4545820351474</v>
+        <v>214.7490106746289</v>
       </c>
       <c r="E45">
-        <v>216.711</v>
+        <v>222.288</v>
       </c>
       <c r="F45">
-        <v>239.811</v>
+        <v>245.388</v>
       </c>
       <c r="G45">
         <v>49.9</v>
@@ -5105,45 +5105,45 @@
         <v>24.1</v>
       </c>
       <c r="M45">
-        <v>48.15404880000001</v>
+        <v>57.86249040000001</v>
       </c>
       <c r="N45">
-        <v>-24.0540488</v>
+        <v>-33.76249040000001</v>
       </c>
       <c r="O45">
         <v>-0</v>
       </c>
       <c r="P45">
-        <v>-24.0540488</v>
+        <v>-33.76249040000001</v>
       </c>
       <c r="Q45">
-        <v>-17.75404880000001</v>
+        <v>-27.46249040000001</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.1513342170871855</v>
+        <v>0.1532187566780281</v>
       </c>
       <c r="T45">
-        <v>2.057058321764213</v>
+        <v>2.093791506081431</v>
       </c>
       <c r="U45">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V45">
         <v>0</v>
       </c>
       <c r="W45">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y45">
-        <v>0.5004771270655854</v>
+        <v>0.4165047137342017</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5151,22 +5151,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1895545037396958</v>
+        <v>0.1914545037396957</v>
       </c>
       <c r="C46">
-        <v>19.26101067462889</v>
+        <v>10.88270271774633</v>
       </c>
       <c r="D46">
-        <v>214.7490106746289</v>
+        <v>211.9477027177464</v>
       </c>
       <c r="E46">
-        <v>222.288</v>
+        <v>227.865</v>
       </c>
       <c r="F46">
-        <v>245.388</v>
+        <v>250.965</v>
       </c>
       <c r="G46">
         <v>49.9</v>
@@ -5187,28 +5187,28 @@
         <v>24.1</v>
       </c>
       <c r="M46">
-        <v>57.86249040000001</v>
+        <v>59.17754700000001</v>
       </c>
       <c r="N46">
-        <v>-33.76249040000001</v>
+        <v>-35.07754700000001</v>
       </c>
       <c r="O46">
         <v>-0</v>
       </c>
       <c r="P46">
-        <v>-33.76249040000001</v>
+        <v>-35.07754700000001</v>
       </c>
       <c r="Q46">
-        <v>-27.46249040000001</v>
+        <v>-28.77754700000001</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1532187566780281</v>
+        <v>0.155171824981265</v>
       </c>
       <c r="T46">
-        <v>2.093791506081431</v>
+        <v>2.131860442555639</v>
       </c>
       <c r="U46">
         <v>0.2358</v>
@@ -5225,7 +5225,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>0.4165047137342017</v>
+        <v>0.4072490534289973</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5233,22 +5233,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1914545037396957</v>
+        <v>0.1933545037396958</v>
       </c>
       <c r="C47">
-        <v>10.88270271774633</v>
+        <v>2.576537392680166</v>
       </c>
       <c r="D47">
-        <v>211.9477027177464</v>
+        <v>209.2185373926802</v>
       </c>
       <c r="E47">
-        <v>227.865</v>
+        <v>233.442</v>
       </c>
       <c r="F47">
-        <v>250.965</v>
+        <v>256.542</v>
       </c>
       <c r="G47">
         <v>49.9</v>
@@ -5269,28 +5269,28 @@
         <v>24.1</v>
       </c>
       <c r="M47">
-        <v>59.17754700000001</v>
+        <v>60.49260360000001</v>
       </c>
       <c r="N47">
-        <v>-35.07754700000001</v>
+        <v>-36.39260360000001</v>
       </c>
       <c r="O47">
         <v>-0</v>
       </c>
       <c r="P47">
-        <v>-35.07754700000001</v>
+        <v>-36.39260360000001</v>
       </c>
       <c r="Q47">
-        <v>-28.77754700000001</v>
+        <v>-30.09260360000001</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.155171824981265</v>
+        <v>0.1571972291475847</v>
       </c>
       <c r="T47">
-        <v>2.131860442555639</v>
+        <v>2.171339339640002</v>
       </c>
       <c r="U47">
         <v>0.2358</v>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>0.4072490534289973</v>
+        <v>0.3983958131370625</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5315,22 +5315,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1933545037396958</v>
+        <v>0.1952545037396958</v>
       </c>
       <c r="C48">
-        <v>2.576537392680166</v>
+        <v>-5.660236726529035</v>
       </c>
       <c r="D48">
-        <v>209.2185373926802</v>
+        <v>206.558763273471</v>
       </c>
       <c r="E48">
-        <v>233.442</v>
+        <v>239.019</v>
       </c>
       <c r="F48">
-        <v>256.542</v>
+        <v>262.119</v>
       </c>
       <c r="G48">
         <v>49.9</v>
@@ -5351,28 +5351,28 @@
         <v>24.1</v>
       </c>
       <c r="M48">
-        <v>60.49260360000001</v>
+        <v>61.80766020000001</v>
       </c>
       <c r="N48">
-        <v>-36.39260360000001</v>
+        <v>-37.70766020000001</v>
       </c>
       <c r="O48">
         <v>-0</v>
       </c>
       <c r="P48">
-        <v>-36.39260360000001</v>
+        <v>-37.70766020000001</v>
       </c>
       <c r="Q48">
-        <v>-30.09260360000001</v>
+        <v>-31.40766020000001</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1571972291475847</v>
+        <v>0.1592990636598033</v>
       </c>
       <c r="T48">
-        <v>2.171339339640002</v>
+        <v>2.212308006425663</v>
       </c>
       <c r="U48">
         <v>0.2358</v>
@@ -5389,7 +5389,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.3983958131370625</v>
+        <v>0.3899193064745718</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5397,22 +5397,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1952545037396958</v>
+        <v>0.1971545037396958</v>
       </c>
       <c r="C49">
-        <v>-5.660236726529035</v>
+        <v>-13.83023290782901</v>
       </c>
       <c r="D49">
-        <v>206.558763273471</v>
+        <v>203.965767092171</v>
       </c>
       <c r="E49">
-        <v>239.019</v>
+        <v>244.596</v>
       </c>
       <c r="F49">
-        <v>262.119</v>
+        <v>267.696</v>
       </c>
       <c r="G49">
         <v>49.9</v>
@@ -5433,28 +5433,28 @@
         <v>24.1</v>
       </c>
       <c r="M49">
-        <v>61.80766020000001</v>
+        <v>63.12271680000001</v>
       </c>
       <c r="N49">
-        <v>-37.70766020000001</v>
+        <v>-39.0227168</v>
       </c>
       <c r="O49">
         <v>-0</v>
       </c>
       <c r="P49">
-        <v>-37.70766020000001</v>
+        <v>-39.0227168</v>
       </c>
       <c r="Q49">
-        <v>-31.40766020000001</v>
+        <v>-32.72271680000001</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1592990636598033</v>
+        <v>0.1614817379609534</v>
       </c>
       <c r="T49">
-        <v>2.212308006425663</v>
+        <v>2.254852391164618</v>
       </c>
       <c r="U49">
         <v>0.2358</v>
@@ -5471,7 +5471,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.3899193064745718</v>
+        <v>0.381795987589685</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5479,22 +5479,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1971545037396958</v>
+        <v>0.1990545037396957</v>
       </c>
       <c r="C50">
-        <v>-13.83023290782901</v>
+        <v>-21.93593482534885</v>
       </c>
       <c r="D50">
-        <v>203.965767092171</v>
+        <v>201.4370651746512</v>
       </c>
       <c r="E50">
-        <v>244.596</v>
+        <v>250.173</v>
       </c>
       <c r="F50">
-        <v>267.696</v>
+        <v>273.273</v>
       </c>
       <c r="G50">
         <v>49.9</v>
@@ -5515,28 +5515,28 @@
         <v>24.1</v>
       </c>
       <c r="M50">
-        <v>63.12271680000001</v>
+        <v>64.43777340000001</v>
       </c>
       <c r="N50">
-        <v>-39.0227168</v>
+        <v>-40.33777340000001</v>
       </c>
       <c r="O50">
         <v>-0</v>
       </c>
       <c r="P50">
-        <v>-39.0227168</v>
+        <v>-40.33777340000001</v>
       </c>
       <c r="Q50">
-        <v>-32.72271680000001</v>
+        <v>-34.03777340000001</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1614817379609534</v>
+        <v>0.1637500073327368</v>
       </c>
       <c r="T50">
-        <v>2.254852391164618</v>
+        <v>2.299065183148238</v>
       </c>
       <c r="U50">
         <v>0.2358</v>
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.381795987589685</v>
+        <v>0.3740042327409159</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5561,22 +5561,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1990545037396957</v>
+        <v>0.2009545037396958</v>
       </c>
       <c r="C51">
-        <v>-21.93593482534885</v>
+        <v>-29.97970449433603</v>
       </c>
       <c r="D51">
-        <v>201.4370651746512</v>
+        <v>198.970295505664</v>
       </c>
       <c r="E51">
-        <v>250.173</v>
+        <v>255.75</v>
       </c>
       <c r="F51">
-        <v>273.273</v>
+        <v>278.85</v>
       </c>
       <c r="G51">
         <v>49.9</v>
@@ -5597,28 +5597,28 @@
         <v>24.1</v>
       </c>
       <c r="M51">
-        <v>64.43777340000001</v>
+        <v>65.75283</v>
       </c>
       <c r="N51">
-        <v>-40.33777340000001</v>
+        <v>-41.65283</v>
       </c>
       <c r="O51">
         <v>-0</v>
       </c>
       <c r="P51">
-        <v>-40.33777340000001</v>
+        <v>-41.65283</v>
       </c>
       <c r="Q51">
-        <v>-34.03777340000001</v>
+        <v>-35.35283</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1637500073327368</v>
+        <v>0.1661090074793915</v>
       </c>
       <c r="T51">
-        <v>2.299065183148238</v>
+        <v>2.345046486811203</v>
       </c>
       <c r="U51">
         <v>0.2358</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.3740042327409159</v>
+        <v>0.3665241480860976</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.2009545037396958</v>
+        <v>0.2028545037396958</v>
       </c>
       <c r="C52">
-        <v>-29.97970449433603</v>
+        <v>-37.96378963012648</v>
       </c>
       <c r="D52">
-        <v>198.970295505664</v>
+        <v>196.5632103698735</v>
       </c>
       <c r="E52">
-        <v>255.75</v>
+        <v>261.327</v>
       </c>
       <c r="F52">
-        <v>278.85</v>
+        <v>284.427</v>
       </c>
       <c r="G52">
         <v>49.9</v>
@@ -5679,28 +5679,28 @@
         <v>24.1</v>
       </c>
       <c r="M52">
-        <v>65.75283</v>
+        <v>67.06788660000001</v>
       </c>
       <c r="N52">
-        <v>-41.65283</v>
+        <v>-42.96788660000001</v>
       </c>
       <c r="O52">
         <v>-0</v>
       </c>
       <c r="P52">
-        <v>-41.65283</v>
+        <v>-42.96788660000001</v>
       </c>
       <c r="Q52">
-        <v>-35.35283</v>
+        <v>-36.66788660000001</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1661090074793915</v>
+        <v>0.1685642933463179</v>
       </c>
       <c r="T52">
-        <v>2.345046486811203</v>
+        <v>2.392904578378778</v>
       </c>
       <c r="U52">
         <v>0.2358</v>
@@ -5717,7 +5717,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.3665241480860976</v>
+        <v>0.3593374000844094</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5725,22 +5725,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.2028545037396958</v>
+        <v>0.2047545037396958</v>
       </c>
       <c r="C53">
-        <v>-37.96378963012648</v>
+        <v>-45.89033047933927</v>
       </c>
       <c r="D53">
-        <v>196.5632103698735</v>
+        <v>194.2136695206607</v>
       </c>
       <c r="E53">
-        <v>261.327</v>
+        <v>266.904</v>
       </c>
       <c r="F53">
-        <v>284.427</v>
+        <v>290.004</v>
       </c>
       <c r="G53">
         <v>49.9</v>
@@ -5761,28 +5761,28 @@
         <v>24.1</v>
       </c>
       <c r="M53">
-        <v>67.06788660000001</v>
+        <v>68.38294320000001</v>
       </c>
       <c r="N53">
-        <v>-42.96788660000001</v>
+        <v>-44.28294320000001</v>
       </c>
       <c r="O53">
         <v>-0</v>
       </c>
       <c r="P53">
-        <v>-42.96788660000001</v>
+        <v>-44.28294320000001</v>
       </c>
       <c r="Q53">
-        <v>-36.66788660000001</v>
+        <v>-37.98294320000002</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1685642933463179</v>
+        <v>0.1711218827910329</v>
       </c>
       <c r="T53">
-        <v>2.392904578378778</v>
+        <v>2.442756757095003</v>
       </c>
       <c r="U53">
         <v>0.2358</v>
@@ -5799,7 +5799,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.3593374000844094</v>
+        <v>0.3524270654674014</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5807,22 +5807,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.2047545037396958</v>
+        <v>0.2066545037396958</v>
       </c>
       <c r="C54">
-        <v>-45.89033047933927</v>
+        <v>-53.76136616693432</v>
       </c>
       <c r="D54">
-        <v>194.2136695206607</v>
+        <v>191.9196338330657</v>
       </c>
       <c r="E54">
-        <v>266.904</v>
+        <v>272.481</v>
       </c>
       <c r="F54">
-        <v>290.004</v>
+        <v>295.581</v>
       </c>
       <c r="G54">
         <v>49.9</v>
@@ -5843,28 +5843,28 @@
         <v>24.1</v>
       </c>
       <c r="M54">
-        <v>68.38294320000001</v>
+        <v>69.69799980000001</v>
       </c>
       <c r="N54">
-        <v>-44.28294320000001</v>
+        <v>-45.5979998</v>
       </c>
       <c r="O54">
         <v>-0</v>
       </c>
       <c r="P54">
-        <v>-44.28294320000001</v>
+        <v>-45.5979998</v>
       </c>
       <c r="Q54">
-        <v>-37.98294320000002</v>
+        <v>-39.29799980000001</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1711218827910329</v>
+        <v>0.1737883058291399</v>
       </c>
       <c r="T54">
-        <v>2.442756757095003</v>
+        <v>2.494730305118301</v>
       </c>
       <c r="U54">
         <v>0.2358</v>
@@ -5881,7 +5881,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>0.3524270654674014</v>
+        <v>0.3457774981944317</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5889,22 +5889,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2066545037396958</v>
+        <v>0.2085545037396958</v>
       </c>
       <c r="C55">
-        <v>-53.76136616693432</v>
+        <v>-61.57884059869585</v>
       </c>
       <c r="D55">
-        <v>191.9196338330657</v>
+        <v>189.6791594013042</v>
       </c>
       <c r="E55">
-        <v>272.481</v>
+        <v>278.058</v>
       </c>
       <c r="F55">
-        <v>295.581</v>
+        <v>301.1580000000001</v>
       </c>
       <c r="G55">
         <v>49.9</v>
@@ -5925,28 +5925,28 @@
         <v>24.1</v>
       </c>
       <c r="M55">
-        <v>69.69799980000001</v>
+        <v>71.01305640000002</v>
       </c>
       <c r="N55">
-        <v>-45.5979998</v>
+        <v>-46.91305640000002</v>
       </c>
       <c r="O55">
         <v>-0</v>
       </c>
       <c r="P55">
-        <v>-45.5979998</v>
+        <v>-46.91305640000002</v>
       </c>
       <c r="Q55">
-        <v>-39.29799980000001</v>
+        <v>-40.61305640000003</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1737883058291399</v>
+        <v>0.1765706603036864</v>
       </c>
       <c r="T55">
-        <v>2.494730305118301</v>
+        <v>2.548963572620873</v>
       </c>
       <c r="U55">
         <v>0.2358</v>
@@ -5963,7 +5963,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.3457774981944317</v>
+        <v>0.339374211190831</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5971,22 +5971,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2085545037396958</v>
+        <v>0.2104545037396958</v>
       </c>
       <c r="C56">
-        <v>-61.57884059869585</v>
+        <v>-69.34460795505211</v>
       </c>
       <c r="D56">
-        <v>189.6791594013042</v>
+        <v>187.490392044948</v>
       </c>
       <c r="E56">
-        <v>278.058</v>
+        <v>283.635</v>
       </c>
       <c r="F56">
-        <v>301.1580000000001</v>
+        <v>306.7350000000001</v>
       </c>
       <c r="G56">
         <v>49.9</v>
@@ -6007,28 +6007,28 @@
         <v>24.1</v>
       </c>
       <c r="M56">
-        <v>71.01305640000002</v>
+        <v>72.32811300000002</v>
       </c>
       <c r="N56">
-        <v>-46.91305640000002</v>
+        <v>-48.22811300000001</v>
       </c>
       <c r="O56">
         <v>-0</v>
       </c>
       <c r="P56">
-        <v>-46.91305640000002</v>
+        <v>-48.22811300000001</v>
       </c>
       <c r="Q56">
-        <v>-40.61305640000003</v>
+        <v>-41.92811300000002</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1765706603036864</v>
+        <v>0.1794766749771017</v>
       </c>
       <c r="T56">
-        <v>2.548963572620873</v>
+        <v>2.605607207568003</v>
       </c>
       <c r="U56">
         <v>0.2358</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.339374211190831</v>
+        <v>0.3332037709873614</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -6053,22 +6053,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2104545037396958</v>
+        <v>0.2123545037396958</v>
       </c>
       <c r="C57">
-        <v>-69.34460795505211</v>
+        <v>-77.06043780886469</v>
       </c>
       <c r="D57">
-        <v>187.490392044948</v>
+        <v>185.3515621911354</v>
       </c>
       <c r="E57">
-        <v>283.635</v>
+        <v>289.212</v>
       </c>
       <c r="F57">
-        <v>306.7350000000001</v>
+        <v>312.3120000000001</v>
       </c>
       <c r="G57">
         <v>49.9</v>
@@ -6089,28 +6089,28 @@
         <v>24.1</v>
       </c>
       <c r="M57">
-        <v>72.32811300000002</v>
+        <v>73.64316960000002</v>
       </c>
       <c r="N57">
-        <v>-48.22811300000001</v>
+        <v>-49.54316960000002</v>
       </c>
       <c r="O57">
         <v>-0</v>
       </c>
       <c r="P57">
-        <v>-48.22811300000001</v>
+        <v>-49.54316960000002</v>
       </c>
       <c r="Q57">
-        <v>-41.92811300000002</v>
+        <v>-43.24316960000002</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1794766749771017</v>
+        <v>0.1825147812265813</v>
       </c>
       <c r="T57">
-        <v>2.605607207568003</v>
+        <v>2.664825553194549</v>
       </c>
       <c r="U57">
         <v>0.2358</v>
@@ -6127,7 +6127,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.3332037709873614</v>
+        <v>0.3272537036483013</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6135,22 +6135,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2123545037396958</v>
+        <v>0.2142545037396958</v>
       </c>
       <c r="C58">
-        <v>-77.06043780886469</v>
+        <v>-84.7280198968767</v>
       </c>
       <c r="D58">
-        <v>185.3515621911354</v>
+        <v>183.2609801031234</v>
       </c>
       <c r="E58">
-        <v>289.212</v>
+        <v>294.789</v>
       </c>
       <c r="F58">
-        <v>312.3120000000001</v>
+        <v>317.8890000000001</v>
       </c>
       <c r="G58">
         <v>49.9</v>
@@ -6171,28 +6171,28 @@
         <v>24.1</v>
       </c>
       <c r="M58">
-        <v>73.64316960000002</v>
+        <v>74.95822620000001</v>
       </c>
       <c r="N58">
-        <v>-49.54316960000002</v>
+        <v>-50.85822620000001</v>
       </c>
       <c r="O58">
         <v>-0</v>
       </c>
       <c r="P58">
-        <v>-49.54316960000002</v>
+        <v>-50.85822620000001</v>
       </c>
       <c r="Q58">
-        <v>-43.24316960000002</v>
+        <v>-44.55822620000001</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1825147812265813</v>
+        <v>0.1856941947434785</v>
       </c>
       <c r="T58">
-        <v>2.664825553194549</v>
+        <v>2.726798240478144</v>
       </c>
       <c r="U58">
         <v>0.2358</v>
@@ -6209,7 +6209,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.3272537036483013</v>
+        <v>0.32151241060184</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6217,22 +6217,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2142545037396958</v>
+        <v>0.2161545037396958</v>
       </c>
       <c r="C59">
-        <v>-84.7280198968767</v>
+        <v>-92.34896857185848</v>
       </c>
       <c r="D59">
-        <v>183.2609801031234</v>
+        <v>181.2170314281416</v>
       </c>
       <c r="E59">
-        <v>294.789</v>
+        <v>300.366</v>
       </c>
       <c r="F59">
-        <v>317.8890000000001</v>
+        <v>323.4660000000001</v>
       </c>
       <c r="G59">
         <v>49.9</v>
@@ -6253,28 +6253,28 @@
         <v>24.1</v>
       </c>
       <c r="M59">
-        <v>74.95822620000001</v>
+        <v>76.27328280000002</v>
       </c>
       <c r="N59">
-        <v>-50.85822620000001</v>
+        <v>-52.17328280000002</v>
       </c>
       <c r="O59">
         <v>-0</v>
       </c>
       <c r="P59">
-        <v>-50.85822620000001</v>
+        <v>-52.17328280000002</v>
       </c>
       <c r="Q59">
-        <v>-44.55822620000001</v>
+        <v>-45.87328280000002</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1856941947434785</v>
+        <v>0.1890250089040375</v>
       </c>
       <c r="T59">
-        <v>2.726798240478144</v>
+        <v>2.791722008108575</v>
       </c>
       <c r="U59">
         <v>0.2358</v>
@@ -6291,7 +6291,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.32151241060184</v>
+        <v>0.3159690931776703</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6299,22 +6299,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2161545037396957</v>
+        <v>0.2180545037396958</v>
       </c>
       <c r="C60">
-        <v>-92.34896857185842</v>
+        <v>-99.92482696010575</v>
       </c>
       <c r="D60">
-        <v>181.2170314281416</v>
+        <v>179.2181730398943</v>
       </c>
       <c r="E60">
-        <v>300.366</v>
+        <v>305.943</v>
       </c>
       <c r="F60">
-        <v>323.466</v>
+        <v>329.043</v>
       </c>
       <c r="G60">
         <v>49.9</v>
@@ -6335,28 +6335,28 @@
         <v>24.1</v>
       </c>
       <c r="M60">
-        <v>76.2732828</v>
+        <v>77.58833940000001</v>
       </c>
       <c r="N60">
-        <v>-52.1732828</v>
+        <v>-53.48833940000001</v>
       </c>
       <c r="O60">
         <v>-0</v>
       </c>
       <c r="P60">
-        <v>-52.1732828</v>
+        <v>-53.48833940000001</v>
       </c>
       <c r="Q60">
-        <v>-45.87328280000001</v>
+        <v>-47.18833940000001</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1890250089040375</v>
+        <v>0.192518301804136</v>
       </c>
       <c r="T60">
-        <v>2.791722008108574</v>
+        <v>2.859812788794149</v>
       </c>
       <c r="U60">
         <v>0.2358</v>
@@ -6373,7 +6373,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.3159690931776703</v>
+        <v>0.3106136848187268</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6381,22 +6381,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2180545037396958</v>
+        <v>0.2199545037396958</v>
       </c>
       <c r="C61">
-        <v>-99.92482696010575</v>
+        <v>-107.4570708467913</v>
       </c>
       <c r="D61">
-        <v>179.2181730398943</v>
+        <v>177.2629291532087</v>
       </c>
       <c r="E61">
-        <v>305.943</v>
+        <v>311.52</v>
       </c>
       <c r="F61">
-        <v>329.043</v>
+        <v>334.62</v>
       </c>
       <c r="G61">
         <v>49.9</v>
@@ -6417,28 +6417,28 @@
         <v>24.1</v>
       </c>
       <c r="M61">
-        <v>77.58833940000001</v>
+        <v>78.903396</v>
       </c>
       <c r="N61">
-        <v>-53.48833940000001</v>
+        <v>-54.803396</v>
       </c>
       <c r="O61">
         <v>-0</v>
       </c>
       <c r="P61">
-        <v>-53.48833940000001</v>
+        <v>-54.803396</v>
       </c>
       <c r="Q61">
-        <v>-47.18833940000001</v>
+        <v>-48.503396</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.192518301804136</v>
+        <v>0.1961862593492394</v>
       </c>
       <c r="T61">
-        <v>2.859812788794149</v>
+        <v>2.931308108514004</v>
       </c>
       <c r="U61">
         <v>0.2358</v>
@@ -6455,7 +6455,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.3106136848187268</v>
+        <v>0.305436790071748</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6463,22 +6463,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2199545037396958</v>
+        <v>0.2218545037396958</v>
       </c>
       <c r="C62">
-        <v>-107.4570708467913</v>
+        <v>-114.9471123097298</v>
       </c>
       <c r="D62">
-        <v>177.2629291532087</v>
+        <v>175.3498876902702</v>
       </c>
       <c r="E62">
-        <v>311.52</v>
+        <v>317.097</v>
       </c>
       <c r="F62">
-        <v>334.62</v>
+        <v>340.197</v>
       </c>
       <c r="G62">
         <v>49.9</v>
@@ -6499,28 +6499,28 @@
         <v>24.1</v>
       </c>
       <c r="M62">
-        <v>78.903396</v>
+        <v>80.21845260000001</v>
       </c>
       <c r="N62">
-        <v>-54.803396</v>
+        <v>-56.1184526</v>
       </c>
       <c r="O62">
         <v>-0</v>
       </c>
       <c r="P62">
-        <v>-54.803396</v>
+        <v>-56.1184526</v>
       </c>
       <c r="Q62">
-        <v>-48.503396</v>
+        <v>-49.81845260000001</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1961862593492394</v>
+        <v>0.2000423172812712</v>
       </c>
       <c r="T62">
-        <v>2.931308108514004</v>
+        <v>3.006469854886157</v>
       </c>
       <c r="U62">
         <v>0.2358</v>
@@ -6537,7 +6537,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.305436790071748</v>
+        <v>0.3004296295787685</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6545,22 +6545,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2218545037396958</v>
+        <v>0.2237545037396957</v>
       </c>
       <c r="C63">
-        <v>-114.9471123097298</v>
+        <v>-122.3963031203588</v>
       </c>
       <c r="D63">
-        <v>175.3498876902702</v>
+        <v>173.4776968796412</v>
       </c>
       <c r="E63">
-        <v>317.097</v>
+        <v>322.674</v>
       </c>
       <c r="F63">
-        <v>340.197</v>
+        <v>345.774</v>
       </c>
       <c r="G63">
         <v>49.9</v>
@@ -6581,28 +6581,28 @@
         <v>24.1</v>
       </c>
       <c r="M63">
-        <v>80.21845260000001</v>
+        <v>81.5335092</v>
       </c>
       <c r="N63">
-        <v>-56.1184526</v>
+        <v>-57.4335092</v>
       </c>
       <c r="O63">
         <v>-0</v>
       </c>
       <c r="P63">
-        <v>-56.1184526</v>
+        <v>-57.4335092</v>
       </c>
       <c r="Q63">
-        <v>-49.81845260000001</v>
+        <v>-51.1335092</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2000423172812712</v>
+        <v>0.2041013256307783</v>
       </c>
       <c r="T63">
-        <v>3.006469854886157</v>
+        <v>3.08558748264632</v>
       </c>
       <c r="U63">
         <v>0.2358</v>
@@ -6619,7 +6619,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>0.3004296295787685</v>
+        <v>0.2955839903920142</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6627,22 +6627,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2237545037396957</v>
+        <v>0.2256545037396958</v>
       </c>
       <c r="C64">
-        <v>-122.3963031203588</v>
+        <v>-129.8059379291505</v>
       </c>
       <c r="D64">
-        <v>173.4776968796412</v>
+        <v>171.6450620708495</v>
       </c>
       <c r="E64">
-        <v>322.674</v>
+        <v>328.251</v>
       </c>
       <c r="F64">
-        <v>345.774</v>
+        <v>351.3510000000001</v>
       </c>
       <c r="G64">
         <v>49.9</v>
@@ -6663,28 +6663,28 @@
         <v>24.1</v>
       </c>
       <c r="M64">
-        <v>81.5335092</v>
+        <v>82.84856580000002</v>
       </c>
       <c r="N64">
-        <v>-57.4335092</v>
+        <v>-58.74856580000002</v>
       </c>
       <c r="O64">
         <v>-0</v>
       </c>
       <c r="P64">
-        <v>-57.4335092</v>
+        <v>-58.74856580000002</v>
       </c>
       <c r="Q64">
-        <v>-51.1335092</v>
+        <v>-52.44856580000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.2041013256307783</v>
+        <v>0.2083797398370155</v>
       </c>
       <c r="T64">
-        <v>3.08558748264632</v>
+        <v>3.168981738934058</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
@@ -6701,7 +6701,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.2955839903920142</v>
+        <v>0.2908921810207123</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2256545037396958</v>
+        <v>0.2275545037396958</v>
       </c>
       <c r="C65">
-        <v>-129.8059379291505</v>
+        <v>-137.1772572512273</v>
       </c>
       <c r="D65">
-        <v>171.6450620708495</v>
+        <v>169.8507427487727</v>
       </c>
       <c r="E65">
-        <v>328.251</v>
+        <v>333.828</v>
       </c>
       <c r="F65">
-        <v>351.3510000000001</v>
+        <v>356.9280000000001</v>
       </c>
       <c r="G65">
         <v>49.9</v>
@@ -6745,28 +6745,28 @@
         <v>24.1</v>
       </c>
       <c r="M65">
-        <v>82.84856580000002</v>
+        <v>84.16362240000002</v>
       </c>
       <c r="N65">
-        <v>-58.74856580000002</v>
+        <v>-60.06362240000002</v>
       </c>
       <c r="O65">
         <v>-0</v>
       </c>
       <c r="P65">
-        <v>-58.74856580000002</v>
+        <v>-60.06362240000002</v>
       </c>
       <c r="Q65">
-        <v>-52.44856580000002</v>
+        <v>-53.76362240000002</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.2083797398370155</v>
+        <v>0.2128958437213771</v>
       </c>
       <c r="T65">
-        <v>3.168981738934058</v>
+        <v>3.257009009460004</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
@@ -6783,7 +6783,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.2908921810207123</v>
+        <v>0.2863469906922637</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6791,22 +6791,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2275545037396958</v>
+        <v>0.2294545037396958</v>
       </c>
       <c r="C66">
-        <v>-137.1772572512273</v>
+        <v>-144.511450266652</v>
       </c>
       <c r="D66">
-        <v>169.8507427487727</v>
+        <v>168.0935497333481</v>
       </c>
       <c r="E66">
-        <v>333.828</v>
+        <v>339.405</v>
       </c>
       <c r="F66">
-        <v>356.9280000000001</v>
+        <v>362.5050000000001</v>
       </c>
       <c r="G66">
         <v>49.9</v>
@@ -6827,28 +6827,28 @@
         <v>24.1</v>
       </c>
       <c r="M66">
-        <v>84.16362240000002</v>
+        <v>85.47867900000001</v>
       </c>
       <c r="N66">
-        <v>-60.06362240000002</v>
+        <v>-61.37867900000001</v>
       </c>
       <c r="O66">
         <v>-0</v>
       </c>
       <c r="P66">
-        <v>-60.06362240000002</v>
+        <v>-61.37867900000001</v>
       </c>
       <c r="Q66">
-        <v>-53.76362240000002</v>
+        <v>-55.07867900000002</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.2128958437213771</v>
+        <v>0.2176700106848451</v>
       </c>
       <c r="T66">
-        <v>3.257009009460004</v>
+        <v>3.350066409730291</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
@@ -6865,7 +6865,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.2863469906922637</v>
+        <v>0.2819416523739212</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6873,22 +6873,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2294545037396958</v>
+        <v>0.2313545037396958</v>
       </c>
       <c r="C67">
-        <v>-144.511450266652</v>
+        <v>-151.8096574486744</v>
       </c>
       <c r="D67">
-        <v>168.0935497333481</v>
+        <v>166.3723425513257</v>
       </c>
       <c r="E67">
-        <v>339.405</v>
+        <v>344.982</v>
       </c>
       <c r="F67">
-        <v>362.5050000000001</v>
+        <v>368.0820000000001</v>
       </c>
       <c r="G67">
         <v>49.9</v>
@@ -6909,28 +6909,28 @@
         <v>24.1</v>
       </c>
       <c r="M67">
-        <v>85.47867900000001</v>
+        <v>86.79373560000002</v>
       </c>
       <c r="N67">
-        <v>-61.37867900000001</v>
+        <v>-62.69373560000002</v>
       </c>
       <c r="O67">
         <v>-0</v>
       </c>
       <c r="P67">
-        <v>-61.37867900000001</v>
+        <v>-62.69373560000002</v>
       </c>
       <c r="Q67">
-        <v>-55.07867900000002</v>
+        <v>-56.39373560000002</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.2176700106848451</v>
+        <v>0.2227250109991052</v>
       </c>
       <c r="T67">
-        <v>3.350066409730291</v>
+        <v>3.448597774722357</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
@@ -6947,7 +6947,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.2819416523739212</v>
+        <v>0.2776698091561345</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6955,22 +6955,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2313545037396958</v>
+        <v>0.2332545037396958</v>
       </c>
       <c r="C68">
-        <v>-151.8096574486744</v>
+        <v>-159.0729730321424</v>
       </c>
       <c r="D68">
-        <v>166.3723425513257</v>
+        <v>164.6860269678577</v>
       </c>
       <c r="E68">
-        <v>344.982</v>
+        <v>350.559</v>
       </c>
       <c r="F68">
-        <v>368.0820000000001</v>
+        <v>373.659</v>
       </c>
       <c r="G68">
         <v>49.9</v>
@@ -6991,28 +6991,28 @@
         <v>24.1</v>
       </c>
       <c r="M68">
-        <v>86.79373560000002</v>
+        <v>88.10879220000001</v>
       </c>
       <c r="N68">
-        <v>-62.69373560000002</v>
+        <v>-64.00879220000002</v>
       </c>
       <c r="O68">
         <v>-0</v>
       </c>
       <c r="P68">
-        <v>-62.69373560000002</v>
+        <v>-64.00879220000002</v>
       </c>
       <c r="Q68">
-        <v>-56.39373560000002</v>
+        <v>-57.70879220000002</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.2227250109991052</v>
+        <v>0.228086374968775</v>
       </c>
       <c r="T68">
-        <v>3.448597774722357</v>
+        <v>3.553100737592732</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
@@ -7029,7 +7029,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.2776698091561345</v>
+        <v>0.2735254836463414</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7037,22 +7037,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2332545037396958</v>
+        <v>0.2351545037396958</v>
       </c>
       <c r="C69">
-        <v>-159.0729730321424</v>
+        <v>-166.3024473333033</v>
       </c>
       <c r="D69">
-        <v>164.6860269678577</v>
+        <v>163.0335526666967</v>
       </c>
       <c r="E69">
-        <v>350.559</v>
+        <v>356.136</v>
       </c>
       <c r="F69">
-        <v>373.659</v>
+        <v>379.236</v>
       </c>
       <c r="G69">
         <v>49.9</v>
@@ -7073,28 +7073,28 @@
         <v>24.1</v>
       </c>
       <c r="M69">
-        <v>88.10879220000001</v>
+        <v>89.42384880000002</v>
       </c>
       <c r="N69">
-        <v>-64.00879220000002</v>
+        <v>-65.32384880000001</v>
       </c>
       <c r="O69">
         <v>-0</v>
       </c>
       <c r="P69">
-        <v>-64.00879220000002</v>
+        <v>-65.32384880000001</v>
       </c>
       <c r="Q69">
-        <v>-57.70879220000002</v>
+        <v>-59.02384880000001</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.228086374968775</v>
+        <v>0.2337828241865493</v>
       </c>
       <c r="T69">
-        <v>3.553100737592732</v>
+        <v>3.664135135642505</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
@@ -7111,7 +7111,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.2735254836463414</v>
+        <v>0.2695030500633071</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -7119,22 +7119,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2351545037396958</v>
+        <v>0.2370545037396958</v>
       </c>
       <c r="C70">
-        <v>-166.3024473333033</v>
+        <v>-173.4990889313298</v>
       </c>
       <c r="D70">
-        <v>163.0335526666967</v>
+        <v>161.4139110686702</v>
       </c>
       <c r="E70">
-        <v>356.136</v>
+        <v>361.713</v>
       </c>
       <c r="F70">
-        <v>379.236</v>
+        <v>384.813</v>
       </c>
       <c r="G70">
         <v>49.9</v>
@@ -7155,28 +7155,28 @@
         <v>24.1</v>
       </c>
       <c r="M70">
-        <v>89.42384880000002</v>
+        <v>90.73890540000001</v>
       </c>
       <c r="N70">
-        <v>-65.32384880000001</v>
+        <v>-66.6389054</v>
       </c>
       <c r="O70">
         <v>-0</v>
       </c>
       <c r="P70">
-        <v>-65.32384880000001</v>
+        <v>-66.6389054</v>
       </c>
       <c r="Q70">
-        <v>-59.02384880000001</v>
+        <v>-60.3389054</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.2337828241865493</v>
+        <v>0.2398467862570831</v>
       </c>
       <c r="T70">
-        <v>3.664135135642505</v>
+        <v>3.782333043243876</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
@@ -7193,7 +7193,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.2695030500633071</v>
+        <v>0.2655972087580418</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7201,22 +7201,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2370545037396958</v>
+        <v>0.2389545037396958</v>
       </c>
       <c r="C71">
-        <v>-173.4990889313298</v>
+        <v>-180.6638667210923</v>
       </c>
       <c r="D71">
-        <v>161.4139110686702</v>
+        <v>159.8261332789078</v>
       </c>
       <c r="E71">
-        <v>361.713</v>
+        <v>367.29</v>
       </c>
       <c r="F71">
-        <v>384.813</v>
+        <v>390.39</v>
       </c>
       <c r="G71">
         <v>49.9</v>
@@ -7237,28 +7237,28 @@
         <v>24.1</v>
       </c>
       <c r="M71">
-        <v>90.73890540000001</v>
+        <v>92.05396200000001</v>
       </c>
       <c r="N71">
-        <v>-66.6389054</v>
+        <v>-67.95396200000002</v>
       </c>
       <c r="O71">
         <v>-0</v>
       </c>
       <c r="P71">
-        <v>-66.6389054</v>
+        <v>-67.95396200000002</v>
       </c>
       <c r="Q71">
-        <v>-60.3389054</v>
+        <v>-61.65396200000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.2398467862570831</v>
+        <v>0.2463150124656525</v>
       </c>
       <c r="T71">
-        <v>3.782333043243876</v>
+        <v>3.908410811352006</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
@@ -7275,7 +7275,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.2655972087580418</v>
+        <v>0.261802962918641</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7283,22 +7283,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2389545037396958</v>
+        <v>0.2408545037396958</v>
       </c>
       <c r="C72">
-        <v>-180.6638667210923</v>
+        <v>-187.7977118459563</v>
       </c>
       <c r="D72">
-        <v>159.8261332789078</v>
+        <v>158.2692881540437</v>
       </c>
       <c r="E72">
-        <v>367.29</v>
+        <v>372.8670000000001</v>
       </c>
       <c r="F72">
-        <v>390.39</v>
+        <v>395.9670000000001</v>
       </c>
       <c r="G72">
         <v>49.9</v>
@@ -7319,28 +7319,28 @@
         <v>24.1</v>
       </c>
       <c r="M72">
-        <v>92.05396200000001</v>
+        <v>93.36901860000003</v>
       </c>
       <c r="N72">
-        <v>-67.95396200000002</v>
+        <v>-69.26901860000004</v>
       </c>
       <c r="O72">
         <v>-0</v>
       </c>
       <c r="P72">
-        <v>-67.95396200000002</v>
+        <v>-69.26901860000004</v>
       </c>
       <c r="Q72">
-        <v>-61.65396200000002</v>
+        <v>-62.96901860000004</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.2463150124656525</v>
+        <v>0.2532293232403303</v>
       </c>
       <c r="T72">
-        <v>3.908410811352006</v>
+        <v>4.043183597950351</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
@@ -7357,7 +7357,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.261802962918641</v>
+        <v>0.2581155972437306</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7365,22 +7365,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2408545037396957</v>
+        <v>0.2427545037396958</v>
       </c>
       <c r="C73">
-        <v>-187.7977118459562</v>
+        <v>-194.9015195187076</v>
       </c>
       <c r="D73">
-        <v>158.2692881540437</v>
+        <v>156.7424804812925</v>
       </c>
       <c r="E73">
-        <v>372.867</v>
+        <v>378.444</v>
       </c>
       <c r="F73">
-        <v>395.967</v>
+        <v>401.544</v>
       </c>
       <c r="G73">
         <v>49.9</v>
@@ -7401,28 +7401,28 @@
         <v>24.1</v>
       </c>
       <c r="M73">
-        <v>93.3690186</v>
+        <v>94.68407520000001</v>
       </c>
       <c r="N73">
-        <v>-69.26901860000001</v>
+        <v>-70.5840752</v>
       </c>
       <c r="O73">
         <v>-0</v>
       </c>
       <c r="P73">
-        <v>-69.26901860000001</v>
+        <v>-70.5840752</v>
       </c>
       <c r="Q73">
-        <v>-62.96901860000001</v>
+        <v>-64.2840752</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.2532293232403302</v>
+        <v>0.2606375133560562</v>
       </c>
       <c r="T73">
-        <v>4.04318359795035</v>
+        <v>4.187583012162862</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.2581155972437307</v>
+        <v>0.2545306583931234</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7447,22 +7447,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2427545037396958</v>
+        <v>0.2446545037396958</v>
       </c>
       <c r="C74">
-        <v>-194.9015195187076</v>
+        <v>-201.9761507380854</v>
       </c>
       <c r="D74">
-        <v>156.7424804812925</v>
+        <v>155.2448492619147</v>
       </c>
       <c r="E74">
-        <v>378.444</v>
+        <v>384.021</v>
       </c>
       <c r="F74">
-        <v>401.544</v>
+        <v>407.121</v>
       </c>
       <c r="G74">
         <v>49.9</v>
@@ -7483,28 +7483,28 @@
         <v>24.1</v>
       </c>
       <c r="M74">
-        <v>94.68407520000001</v>
+        <v>95.99913180000001</v>
       </c>
       <c r="N74">
-        <v>-70.5840752</v>
+        <v>-71.89913180000002</v>
       </c>
       <c r="O74">
         <v>-0</v>
       </c>
       <c r="P74">
-        <v>-70.5840752</v>
+        <v>-71.89913180000002</v>
       </c>
       <c r="Q74">
-        <v>-64.2840752</v>
+        <v>-65.59913180000002</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.2606375133560562</v>
+        <v>0.2685944582951694</v>
       </c>
       <c r="T74">
-        <v>4.187583012162862</v>
+        <v>4.342678679280005</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.2545306583931234</v>
+        <v>0.2510439370452722</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7529,22 +7529,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2446545037396958</v>
+        <v>0.2465545037396958</v>
       </c>
       <c r="C75">
-        <v>-201.9761507380854</v>
+        <v>-209.0224339078423</v>
       </c>
       <c r="D75">
-        <v>155.2448492619147</v>
+        <v>153.7755660921577</v>
       </c>
       <c r="E75">
-        <v>384.021</v>
+        <v>389.598</v>
       </c>
       <c r="F75">
-        <v>407.121</v>
+        <v>412.698</v>
       </c>
       <c r="G75">
         <v>49.9</v>
@@ -7565,28 +7565,28 @@
         <v>24.1</v>
       </c>
       <c r="M75">
-        <v>95.99913180000001</v>
+        <v>97.31418840000001</v>
       </c>
       <c r="N75">
-        <v>-71.89913180000002</v>
+        <v>-73.21418840000001</v>
       </c>
       <c r="O75">
         <v>-0</v>
       </c>
       <c r="P75">
-        <v>-71.89913180000002</v>
+        <v>-73.21418840000001</v>
       </c>
       <c r="Q75">
-        <v>-65.59913180000002</v>
+        <v>-66.91418840000001</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2685944582951694</v>
+        <v>0.2771634759219067</v>
       </c>
       <c r="T75">
-        <v>4.342678679280005</v>
+        <v>4.509704782329236</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
@@ -7603,7 +7603,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.2510439370452722</v>
+        <v>0.2476514514095253</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7611,22 +7611,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2465545037396958</v>
+        <v>0.2484545037396957</v>
       </c>
       <c r="C76">
-        <v>-209.0224339078423</v>
+        <v>-216.0411663647256</v>
       </c>
       <c r="D76">
-        <v>153.7755660921577</v>
+        <v>152.3338336352744</v>
       </c>
       <c r="E76">
-        <v>389.598</v>
+        <v>395.175</v>
       </c>
       <c r="F76">
-        <v>412.698</v>
+        <v>418.275</v>
       </c>
       <c r="G76">
         <v>49.9</v>
@@ -7647,28 +7647,28 @@
         <v>24.1</v>
       </c>
       <c r="M76">
-        <v>97.31418840000001</v>
+        <v>98.62924500000001</v>
       </c>
       <c r="N76">
-        <v>-73.21418840000001</v>
+        <v>-74.529245</v>
       </c>
       <c r="O76">
         <v>-0</v>
       </c>
       <c r="P76">
-        <v>-73.21418840000001</v>
+        <v>-74.529245</v>
       </c>
       <c r="Q76">
-        <v>-66.91418840000001</v>
+        <v>-68.22924500000001</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2771634759219067</v>
+        <v>0.286418014958783</v>
       </c>
       <c r="T76">
-        <v>4.509704782329236</v>
+        <v>4.690092973622406</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
@@ -7685,7 +7685,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.2476514514095253</v>
+        <v>0.2443494320573985</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7693,22 +7693,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2484545037396957</v>
+        <v>0.2503545037396958</v>
       </c>
       <c r="C77">
-        <v>-216.0411663647256</v>
+        <v>-223.0331158213034</v>
       </c>
       <c r="D77">
-        <v>152.3338336352744</v>
+        <v>150.9188841786966</v>
       </c>
       <c r="E77">
-        <v>395.175</v>
+        <v>400.752</v>
       </c>
       <c r="F77">
-        <v>418.275</v>
+        <v>423.852</v>
       </c>
       <c r="G77">
         <v>49.9</v>
@@ -7729,28 +7729,28 @@
         <v>24.1</v>
       </c>
       <c r="M77">
-        <v>98.62924500000001</v>
+        <v>99.94430160000002</v>
       </c>
       <c r="N77">
-        <v>-74.529245</v>
+        <v>-75.84430160000002</v>
       </c>
       <c r="O77">
         <v>-0</v>
       </c>
       <c r="P77">
-        <v>-74.529245</v>
+        <v>-75.84430160000002</v>
       </c>
       <c r="Q77">
-        <v>-68.22924500000001</v>
+        <v>-69.54430160000003</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.286418014958783</v>
+        <v>0.2964437655820657</v>
       </c>
       <c r="T77">
-        <v>4.690092973622406</v>
+        <v>4.885513514190007</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
@@ -7767,7 +7767,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.2443494320573985</v>
+        <v>0.2411343079513799</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7775,22 +7775,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2503545037396958</v>
+        <v>0.2522545037396958</v>
       </c>
       <c r="C78">
-        <v>-223.0331158213034</v>
+        <v>-229.9990217291206</v>
       </c>
       <c r="D78">
-        <v>150.9188841786966</v>
+        <v>149.5299782708794</v>
       </c>
       <c r="E78">
-        <v>400.752</v>
+        <v>406.329</v>
       </c>
       <c r="F78">
-        <v>423.852</v>
+        <v>429.429</v>
       </c>
       <c r="G78">
         <v>49.9</v>
@@ -7811,28 +7811,28 @@
         <v>24.1</v>
       </c>
       <c r="M78">
-        <v>99.94430160000002</v>
+        <v>101.2593582</v>
       </c>
       <c r="N78">
-        <v>-75.84430160000002</v>
+        <v>-77.15935820000001</v>
       </c>
       <c r="O78">
         <v>-0</v>
       </c>
       <c r="P78">
-        <v>-75.84430160000002</v>
+        <v>-77.15935820000001</v>
       </c>
       <c r="Q78">
-        <v>-69.54430160000003</v>
+        <v>-70.85935820000002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2964437655820657</v>
+        <v>0.3073413206073728</v>
       </c>
       <c r="T78">
-        <v>4.885513514190007</v>
+        <v>5.097927145241745</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
@@ -7849,7 +7849,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.2411343079513799</v>
+        <v>0.238002693562401</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7857,22 +7857,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2522545037396958</v>
+        <v>0.2541545037396957</v>
       </c>
       <c r="C79">
-        <v>-229.9990217291206</v>
+        <v>-236.9395965672705</v>
       </c>
       <c r="D79">
-        <v>149.5299782708794</v>
+        <v>148.1664034327295</v>
       </c>
       <c r="E79">
-        <v>406.329</v>
+        <v>411.906</v>
       </c>
       <c r="F79">
-        <v>429.429</v>
+        <v>435.006</v>
       </c>
       <c r="G79">
         <v>49.9</v>
@@ -7893,28 +7893,28 @@
         <v>24.1</v>
       </c>
       <c r="M79">
-        <v>101.2593582</v>
+        <v>102.5744148</v>
       </c>
       <c r="N79">
-        <v>-77.15935820000001</v>
+        <v>-78.47441480000001</v>
       </c>
       <c r="O79">
         <v>-0</v>
       </c>
       <c r="P79">
-        <v>-77.15935820000001</v>
+        <v>-78.47441480000001</v>
       </c>
       <c r="Q79">
-        <v>-70.85935820000002</v>
+        <v>-72.17441480000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.3073413206073728</v>
+        <v>0.3192295624531625</v>
       </c>
       <c r="T79">
-        <v>5.097927145241745</v>
+        <v>5.329651106389098</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
@@ -7931,7 +7931,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.238002693562401</v>
+        <v>0.2349513769782677</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7939,22 +7939,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2541545037396957</v>
+        <v>0.2560545037396957</v>
       </c>
       <c r="C80">
-        <v>-236.9395965672705</v>
+        <v>-243.8555270611006</v>
       </c>
       <c r="D80">
-        <v>148.1664034327295</v>
+        <v>146.8274729388995</v>
       </c>
       <c r="E80">
-        <v>411.906</v>
+        <v>417.4830000000001</v>
       </c>
       <c r="F80">
-        <v>435.006</v>
+        <v>440.5830000000001</v>
       </c>
       <c r="G80">
         <v>49.9</v>
@@ -7975,28 +7975,28 @@
         <v>24.1</v>
       </c>
       <c r="M80">
-        <v>102.5744148</v>
+        <v>103.8894714</v>
       </c>
       <c r="N80">
-        <v>-78.47441480000001</v>
+        <v>-79.78947140000002</v>
       </c>
       <c r="O80">
         <v>-0</v>
       </c>
       <c r="P80">
-        <v>-78.47441480000001</v>
+        <v>-79.78947140000002</v>
       </c>
       <c r="Q80">
-        <v>-72.17441480000001</v>
+        <v>-73.48947140000003</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.3192295624531625</v>
+        <v>0.3322500178080751</v>
       </c>
       <c r="T80">
-        <v>5.329651106389098</v>
+        <v>5.58344401621715</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
@@ -8013,7 +8013,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.2349513769782677</v>
+        <v>0.2319773089152516</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8021,22 +8021,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2560545037396957</v>
+        <v>0.2579545037396958</v>
       </c>
       <c r="C81">
-        <v>-243.8555270611006</v>
+        <v>-250.7474753354309</v>
       </c>
       <c r="D81">
-        <v>146.8274729388995</v>
+        <v>145.5125246645692</v>
       </c>
       <c r="E81">
-        <v>417.4830000000001</v>
+        <v>423.0600000000001</v>
       </c>
       <c r="F81">
-        <v>440.5830000000001</v>
+        <v>446.1600000000001</v>
       </c>
       <c r="G81">
         <v>49.9</v>
@@ -8057,28 +8057,28 @@
         <v>24.1</v>
       </c>
       <c r="M81">
-        <v>103.8894714</v>
+        <v>105.204528</v>
       </c>
       <c r="N81">
-        <v>-79.78947140000002</v>
+        <v>-81.10452800000002</v>
       </c>
       <c r="O81">
         <v>-0</v>
       </c>
       <c r="P81">
-        <v>-79.78947140000002</v>
+        <v>-81.10452800000002</v>
       </c>
       <c r="Q81">
-        <v>-73.48947140000003</v>
+        <v>-74.80452800000002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.3322500178080751</v>
+        <v>0.3465725186984788</v>
       </c>
       <c r="T81">
-        <v>5.58344401621715</v>
+        <v>5.862616217028008</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
@@ -8095,7 +8095,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.2319773089152516</v>
+        <v>0.229077592553811</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -8103,22 +8103,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2579545037396958</v>
+        <v>0.2598545037396958</v>
       </c>
       <c r="C82">
-        <v>-250.7474753354309</v>
+        <v>-257.6160800063557</v>
       </c>
       <c r="D82">
-        <v>145.5125246645692</v>
+        <v>144.2209199936443</v>
       </c>
       <c r="E82">
-        <v>423.0600000000001</v>
+        <v>428.6370000000001</v>
       </c>
       <c r="F82">
-        <v>446.1600000000001</v>
+        <v>451.7370000000001</v>
       </c>
       <c r="G82">
         <v>49.9</v>
@@ -8139,28 +8139,28 @@
         <v>24.1</v>
       </c>
       <c r="M82">
-        <v>105.204528</v>
+        <v>106.5195846</v>
       </c>
       <c r="N82">
-        <v>-81.10452800000002</v>
+        <v>-82.41958460000004</v>
       </c>
       <c r="O82">
         <v>-0</v>
       </c>
       <c r="P82">
-        <v>-81.10452800000002</v>
+        <v>-82.41958460000004</v>
       </c>
       <c r="Q82">
-        <v>-74.80452800000002</v>
+        <v>-76.11958460000004</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.3465725186984788</v>
+        <v>0.3624026512615567</v>
       </c>
       <c r="T82">
-        <v>5.862616217028008</v>
+        <v>6.17117496529264</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
@@ -8177,7 +8177,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.229077592553811</v>
+        <v>0.2262494741272206</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8185,22 +8185,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2598545037396958</v>
+        <v>0.2617545037396958</v>
       </c>
       <c r="C83">
-        <v>-257.6160800063557</v>
+        <v>-264.46195721541</v>
       </c>
       <c r="D83">
-        <v>144.2209199936443</v>
+        <v>142.9520427845901</v>
       </c>
       <c r="E83">
-        <v>428.6370000000001</v>
+        <v>434.2140000000001</v>
       </c>
       <c r="F83">
-        <v>451.7370000000001</v>
+        <v>457.3140000000001</v>
       </c>
       <c r="G83">
         <v>49.9</v>
@@ -8221,28 +8221,28 @@
         <v>24.1</v>
       </c>
       <c r="M83">
-        <v>106.5195846</v>
+        <v>107.8346412</v>
       </c>
       <c r="N83">
-        <v>-82.41958460000004</v>
+        <v>-83.73464120000003</v>
       </c>
       <c r="O83">
         <v>-0</v>
       </c>
       <c r="P83">
-        <v>-82.41958460000004</v>
+        <v>-83.73464120000003</v>
       </c>
       <c r="Q83">
-        <v>-76.11958460000004</v>
+        <v>-77.43464120000003</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.3624026512615567</v>
+        <v>0.3799916874427543</v>
       </c>
       <c r="T83">
-        <v>6.17117496529264</v>
+        <v>6.51401801892001</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
@@ -8259,7 +8259,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.2262494741272206</v>
+        <v>0.2234903341988399</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8267,22 +8267,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2617545037396958</v>
+        <v>0.2636545037396958</v>
       </c>
       <c r="C84">
-        <v>-264.46195721541</v>
+        <v>-271.2857016096193</v>
       </c>
       <c r="D84">
-        <v>142.9520427845901</v>
+        <v>141.7052983903808</v>
       </c>
       <c r="E84">
-        <v>434.2140000000001</v>
+        <v>439.7910000000001</v>
       </c>
       <c r="F84">
-        <v>457.3140000000001</v>
+        <v>462.8910000000001</v>
       </c>
       <c r="G84">
         <v>49.9</v>
@@ -8303,28 +8303,28 @@
         <v>24.1</v>
       </c>
       <c r="M84">
-        <v>107.8346412</v>
+        <v>109.1496978</v>
       </c>
       <c r="N84">
-        <v>-83.73464120000003</v>
+        <v>-85.04969780000002</v>
       </c>
       <c r="O84">
         <v>-0</v>
       </c>
       <c r="P84">
-        <v>-83.73464120000003</v>
+        <v>-85.04969780000002</v>
       </c>
       <c r="Q84">
-        <v>-77.43464120000003</v>
+        <v>-78.74969780000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.3799916874427543</v>
+        <v>0.3996500219982105</v>
       </c>
       <c r="T84">
-        <v>6.51401801892001</v>
+        <v>6.897195549444717</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
@@ -8341,7 +8341,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.2234903341988399</v>
+        <v>0.2207976795699383</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8349,22 +8349,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2636545037396958</v>
+        <v>0.2655545037396958</v>
       </c>
       <c r="C85">
-        <v>-271.2857016096193</v>
+        <v>-278.0878872707089</v>
       </c>
       <c r="D85">
-        <v>141.7052983903808</v>
+        <v>140.4801127292912</v>
       </c>
       <c r="E85">
-        <v>439.7910000000001</v>
+        <v>445.3680000000001</v>
       </c>
       <c r="F85">
-        <v>462.8910000000001</v>
+        <v>468.4680000000001</v>
       </c>
       <c r="G85">
         <v>49.9</v>
@@ -8385,28 +8385,28 @@
         <v>24.1</v>
       </c>
       <c r="M85">
-        <v>109.1496978</v>
+        <v>110.4647544</v>
       </c>
       <c r="N85">
-        <v>-85.04969780000002</v>
+        <v>-86.36475440000001</v>
       </c>
       <c r="O85">
         <v>-0</v>
       </c>
       <c r="P85">
-        <v>-85.04969780000002</v>
+        <v>-86.36475440000001</v>
       </c>
       <c r="Q85">
-        <v>-78.74969780000002</v>
+        <v>-80.06475440000001</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3996500219982105</v>
+        <v>0.4217656483730987</v>
       </c>
       <c r="T85">
-        <v>6.897195549444717</v>
+        <v>7.328270271285013</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
@@ -8423,7 +8423,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.2207976795699383</v>
+        <v>0.2181691357655343</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8431,22 +8431,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2655545037396957</v>
+        <v>0.2674545037396958</v>
       </c>
       <c r="C86">
-        <v>-278.0878872707088</v>
+        <v>-284.8690685965216</v>
       </c>
       <c r="D86">
-        <v>140.4801127292912</v>
+        <v>139.2759314034784</v>
       </c>
       <c r="E86">
-        <v>445.368</v>
+        <v>450.945</v>
       </c>
       <c r="F86">
-        <v>468.468</v>
+        <v>474.045</v>
       </c>
       <c r="G86">
         <v>49.9</v>
@@ -8467,28 +8467,28 @@
         <v>24.1</v>
       </c>
       <c r="M86">
-        <v>110.4647544</v>
+        <v>111.779811</v>
       </c>
       <c r="N86">
-        <v>-86.36475440000001</v>
+        <v>-87.679811</v>
       </c>
       <c r="O86">
         <v>-0</v>
       </c>
       <c r="P86">
-        <v>-86.36475440000001</v>
+        <v>-87.679811</v>
       </c>
       <c r="Q86">
-        <v>-80.06475440000001</v>
+        <v>-81.379811</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.4217656483730984</v>
+        <v>0.446830024931305</v>
       </c>
       <c r="T86">
-        <v>7.328270271285008</v>
+        <v>7.816821622704009</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
@@ -8505,7 +8505,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.2181691357655342</v>
+        <v>0.2156024400506457</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8513,22 +8513,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2674545037396958</v>
+        <v>0.2693545037396958</v>
       </c>
       <c r="C87">
-        <v>-284.8690685965216</v>
+        <v>-291.6297811374899</v>
       </c>
       <c r="D87">
-        <v>139.2759314034784</v>
+        <v>138.0922188625101</v>
       </c>
       <c r="E87">
-        <v>450.945</v>
+        <v>456.522</v>
       </c>
       <c r="F87">
-        <v>474.045</v>
+        <v>479.622</v>
       </c>
       <c r="G87">
         <v>49.9</v>
@@ -8549,28 +8549,28 @@
         <v>24.1</v>
       </c>
       <c r="M87">
-        <v>111.779811</v>
+        <v>113.0948676</v>
       </c>
       <c r="N87">
-        <v>-87.679811</v>
+        <v>-88.99486760000002</v>
       </c>
       <c r="O87">
         <v>-0</v>
       </c>
       <c r="P87">
-        <v>-87.679811</v>
+        <v>-88.99486760000002</v>
       </c>
       <c r="Q87">
-        <v>-81.379811</v>
+        <v>-82.69486760000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.446830024931305</v>
+        <v>0.4754750267121125</v>
       </c>
       <c r="T87">
-        <v>7.816821622704009</v>
+        <v>8.375166024325724</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
@@ -8587,7 +8587,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.2156024400506457</v>
+        <v>0.2130954349337776</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8595,22 +8595,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2693545037396958</v>
+        <v>0.2712545037396957</v>
       </c>
       <c r="C88">
-        <v>-291.6297811374899</v>
+        <v>-298.37054239081</v>
       </c>
       <c r="D88">
-        <v>138.0922188625101</v>
+        <v>136.92845760919</v>
       </c>
       <c r="E88">
-        <v>456.522</v>
+        <v>462.099</v>
       </c>
       <c r="F88">
-        <v>479.622</v>
+        <v>485.199</v>
       </c>
       <c r="G88">
         <v>49.9</v>
@@ -8631,28 +8631,28 @@
         <v>24.1</v>
       </c>
       <c r="M88">
-        <v>113.0948676</v>
+        <v>114.4099242</v>
       </c>
       <c r="N88">
-        <v>-88.99486760000002</v>
+        <v>-90.30992420000001</v>
       </c>
       <c r="O88">
         <v>-0</v>
       </c>
       <c r="P88">
-        <v>-88.99486760000002</v>
+        <v>-90.30992420000001</v>
       </c>
       <c r="Q88">
-        <v>-82.69486760000002</v>
+        <v>-84.00992420000001</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.4754750267121125</v>
+        <v>0.5085269518438135</v>
       </c>
       <c r="T88">
-        <v>8.375166024325724</v>
+        <v>9.019409564658472</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
@@ -8669,7 +8669,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.2130954349337776</v>
+        <v>0.2106460621184468</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8677,22 +8677,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2712545037396957</v>
+        <v>0.2731545037396958</v>
       </c>
       <c r="C89">
-        <v>-298.37054239081</v>
+        <v>-305.0918525547966</v>
       </c>
       <c r="D89">
-        <v>136.92845760919</v>
+        <v>135.7841474452034</v>
       </c>
       <c r="E89">
-        <v>462.099</v>
+        <v>467.676</v>
       </c>
       <c r="F89">
-        <v>485.199</v>
+        <v>490.7760000000001</v>
       </c>
       <c r="G89">
         <v>49.9</v>
@@ -8713,28 +8713,28 @@
         <v>24.1</v>
       </c>
       <c r="M89">
-        <v>114.4099242</v>
+        <v>115.7249808</v>
       </c>
       <c r="N89">
-        <v>-90.30992420000001</v>
+        <v>-91.62498080000003</v>
       </c>
       <c r="O89">
         <v>-0</v>
       </c>
       <c r="P89">
-        <v>-90.30992420000001</v>
+        <v>-91.62498080000003</v>
       </c>
       <c r="Q89">
-        <v>-84.00992420000001</v>
+        <v>-85.32498080000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.5085269518438135</v>
+        <v>0.5470875311641313</v>
       </c>
       <c r="T89">
-        <v>9.019409564658472</v>
+        <v>9.771027028380013</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
@@ -8751,7 +8751,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2106460621184468</v>
+        <v>0.2082523568671008</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8759,22 +8759,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2731545037396958</v>
+        <v>0.2750545037396958</v>
       </c>
       <c r="C90">
-        <v>-305.0918525547966</v>
+        <v>-311.794195245725</v>
       </c>
       <c r="D90">
-        <v>135.7841474452034</v>
+        <v>134.6588047542751</v>
       </c>
       <c r="E90">
-        <v>467.676</v>
+        <v>473.253</v>
       </c>
       <c r="F90">
-        <v>490.7760000000001</v>
+        <v>496.3530000000001</v>
       </c>
       <c r="G90">
         <v>49.9</v>
@@ -8795,28 +8795,28 @@
         <v>24.1</v>
       </c>
       <c r="M90">
-        <v>115.7249808</v>
+        <v>117.0400374</v>
       </c>
       <c r="N90">
-        <v>-91.62498080000003</v>
+        <v>-92.94003740000002</v>
       </c>
       <c r="O90">
         <v>-0</v>
       </c>
       <c r="P90">
-        <v>-91.62498080000003</v>
+        <v>-92.94003740000002</v>
       </c>
       <c r="Q90">
-        <v>-85.32498080000003</v>
+        <v>-86.64003740000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.5470875311641313</v>
+        <v>0.592659124906325</v>
       </c>
       <c r="T90">
-        <v>9.771027028380013</v>
+        <v>10.6593022127782</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
@@ -8833,7 +8833,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2082523568671008</v>
+        <v>0.2059124427449985</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8841,22 +8841,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2750545037396958</v>
+        <v>0.2769545037396958</v>
       </c>
       <c r="C91">
-        <v>-311.794195245725</v>
+        <v>-318.4780381793208</v>
       </c>
       <c r="D91">
-        <v>134.6588047542751</v>
+        <v>133.5519618206793</v>
       </c>
       <c r="E91">
-        <v>473.253</v>
+        <v>478.83</v>
       </c>
       <c r="F91">
-        <v>496.3530000000001</v>
+        <v>501.9300000000001</v>
       </c>
       <c r="G91">
         <v>49.9</v>
@@ -8877,28 +8877,28 @@
         <v>24.1</v>
       </c>
       <c r="M91">
-        <v>117.0400374</v>
+        <v>118.355094</v>
       </c>
       <c r="N91">
-        <v>-92.94003740000002</v>
+        <v>-94.25509400000001</v>
       </c>
       <c r="O91">
         <v>-0</v>
       </c>
       <c r="P91">
-        <v>-92.94003740000002</v>
+        <v>-94.25509400000001</v>
       </c>
       <c r="Q91">
-        <v>-86.64003740000003</v>
+        <v>-87.95509400000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.592659124906325</v>
+        <v>0.6473450373969576</v>
       </c>
       <c r="T91">
-        <v>10.6593022127782</v>
+        <v>11.72523243405602</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
@@ -8915,7 +8915,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2059124427449985</v>
+        <v>0.2036245267144987</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8923,22 +8923,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2769545037396958</v>
+        <v>0.2788545037396958</v>
       </c>
       <c r="C92">
-        <v>-318.4780381793208</v>
+        <v>-325.1438338189138</v>
       </c>
       <c r="D92">
-        <v>133.5519618206793</v>
+        <v>132.4631661810863</v>
       </c>
       <c r="E92">
-        <v>478.83</v>
+        <v>484.407</v>
       </c>
       <c r="F92">
-        <v>501.9300000000001</v>
+        <v>507.5070000000001</v>
       </c>
       <c r="G92">
         <v>49.9</v>
@@ -8959,28 +8959,28 @@
         <v>24.1</v>
       </c>
       <c r="M92">
-        <v>118.355094</v>
+        <v>119.6701506</v>
       </c>
       <c r="N92">
-        <v>-94.25509400000001</v>
+        <v>-95.57015060000001</v>
       </c>
       <c r="O92">
         <v>-0</v>
       </c>
       <c r="P92">
-        <v>-94.25509400000001</v>
+        <v>-95.57015060000001</v>
       </c>
       <c r="Q92">
-        <v>-87.95509400000002</v>
+        <v>-89.27015060000001</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.6473450373969576</v>
+        <v>0.7141833748855085</v>
       </c>
       <c r="T92">
-        <v>11.72523243405602</v>
+        <v>13.02803603784002</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
@@ -8997,7 +8997,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.2036245267144987</v>
+        <v>0.2013868945528009</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9005,22 +9005,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2788545037396958</v>
+        <v>0.2807545037396958</v>
       </c>
       <c r="C93">
-        <v>-325.1438338189138</v>
+        <v>-331.7920199921438</v>
       </c>
       <c r="D93">
-        <v>132.4631661810863</v>
+        <v>131.3919800078563</v>
       </c>
       <c r="E93">
-        <v>484.407</v>
+        <v>489.984</v>
       </c>
       <c r="F93">
-        <v>507.5070000000001</v>
+        <v>513.0840000000001</v>
       </c>
       <c r="G93">
         <v>49.9</v>
@@ -9041,28 +9041,28 @@
         <v>24.1</v>
       </c>
       <c r="M93">
-        <v>119.6701506</v>
+        <v>120.9852072</v>
       </c>
       <c r="N93">
-        <v>-95.57015060000001</v>
+        <v>-96.88520720000002</v>
       </c>
       <c r="O93">
         <v>-0</v>
       </c>
       <c r="P93">
-        <v>-95.57015060000001</v>
+        <v>-96.88520720000002</v>
       </c>
       <c r="Q93">
-        <v>-89.27015060000001</v>
+        <v>-90.58520720000003</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.7141833748855085</v>
+        <v>0.7977312967461972</v>
       </c>
       <c r="T93">
-        <v>13.02803603784002</v>
+        <v>14.65654054257003</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
@@ -9079,7 +9079,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2013868945528009</v>
+        <v>0.1991979065685312</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -9087,22 +9087,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2807545037396958</v>
+        <v>0.2826545037396958</v>
       </c>
       <c r="C94">
-        <v>-331.7920199921438</v>
+        <v>-338.4230204779833</v>
       </c>
       <c r="D94">
-        <v>131.3919800078563</v>
+        <v>130.3379795220168</v>
       </c>
       <c r="E94">
-        <v>489.984</v>
+        <v>495.561</v>
       </c>
       <c r="F94">
-        <v>513.0840000000001</v>
+        <v>518.6610000000001</v>
       </c>
       <c r="G94">
         <v>49.9</v>
@@ -9123,28 +9123,28 @@
         <v>24.1</v>
       </c>
       <c r="M94">
-        <v>120.9852072</v>
+        <v>122.3002638</v>
       </c>
       <c r="N94">
-        <v>-96.88520720000002</v>
+        <v>-98.20026380000002</v>
       </c>
       <c r="O94">
         <v>-0</v>
       </c>
       <c r="P94">
-        <v>-96.88520720000002</v>
+        <v>-98.20026380000002</v>
       </c>
       <c r="Q94">
-        <v>-90.58520720000003</v>
+        <v>-91.90026380000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.7977312967461972</v>
+        <v>0.9051500534242256</v>
       </c>
       <c r="T94">
-        <v>14.65654054257003</v>
+        <v>16.75033204865146</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
@@ -9161,7 +9161,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.1991979065685312</v>
+        <v>0.1970559935946762</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9169,22 +9169,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2826545037396958</v>
+        <v>0.2845545037396958</v>
       </c>
       <c r="C95">
-        <v>-338.4230204779833</v>
+        <v>-345.0372455657321</v>
       </c>
       <c r="D95">
-        <v>130.3379795220168</v>
+        <v>129.300754434268</v>
       </c>
       <c r="E95">
-        <v>495.561</v>
+        <v>501.138</v>
       </c>
       <c r="F95">
-        <v>518.6610000000001</v>
+        <v>524.2380000000001</v>
       </c>
       <c r="G95">
         <v>49.9</v>
@@ -9205,28 +9205,28 @@
         <v>24.1</v>
       </c>
       <c r="M95">
-        <v>122.3002638</v>
+        <v>123.6153204</v>
       </c>
       <c r="N95">
-        <v>-98.20026380000002</v>
+        <v>-99.51532040000001</v>
       </c>
       <c r="O95">
         <v>-0</v>
       </c>
       <c r="P95">
-        <v>-98.20026380000002</v>
+        <v>-99.51532040000001</v>
       </c>
       <c r="Q95">
-        <v>-91.90026380000002</v>
+        <v>-93.21532040000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.9051500534242256</v>
+        <v>1.048375062328263</v>
       </c>
       <c r="T95">
-        <v>16.75033204865146</v>
+        <v>19.54205405676004</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
@@ -9243,7 +9243,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.1970559935946762</v>
+        <v>0.194959653237286</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9251,22 +9251,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2845545037396958</v>
+        <v>0.2864545037396958</v>
       </c>
       <c r="C96">
-        <v>-345.0372455657321</v>
+        <v>-351.6350925875308</v>
       </c>
       <c r="D96">
-        <v>129.300754434268</v>
+        <v>128.2799074124693</v>
       </c>
       <c r="E96">
-        <v>501.138</v>
+        <v>506.715</v>
       </c>
       <c r="F96">
-        <v>524.2380000000001</v>
+        <v>529.8150000000001</v>
       </c>
       <c r="G96">
         <v>49.9</v>
@@ -9287,28 +9287,28 @@
         <v>24.1</v>
       </c>
       <c r="M96">
-        <v>123.6153204</v>
+        <v>124.930377</v>
       </c>
       <c r="N96">
-        <v>-99.51532040000001</v>
+        <v>-100.830377</v>
       </c>
       <c r="O96">
         <v>-0</v>
       </c>
       <c r="P96">
-        <v>-99.51532040000001</v>
+        <v>-100.830377</v>
       </c>
       <c r="Q96">
-        <v>-93.21532040000001</v>
+        <v>-94.53037700000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.048375062328263</v>
+        <v>1.248890074793917</v>
       </c>
       <c r="T96">
-        <v>19.54205405676004</v>
+        <v>23.45046486811206</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.194959653237286</v>
+        <v>0.1929074463611039</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9333,22 +9333,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2864545037396958</v>
+        <v>0.2883545037396957</v>
       </c>
       <c r="C97">
-        <v>-351.6350925875308</v>
+        <v>-358.2169464258469</v>
       </c>
       <c r="D97">
-        <v>128.2799074124693</v>
+        <v>127.2750535741532</v>
       </c>
       <c r="E97">
-        <v>506.715</v>
+        <v>512.292</v>
       </c>
       <c r="F97">
-        <v>529.8150000000001</v>
+        <v>535.3920000000001</v>
       </c>
       <c r="G97">
         <v>49.9</v>
@@ -9369,28 +9369,28 @@
         <v>24.1</v>
       </c>
       <c r="M97">
-        <v>124.930377</v>
+        <v>126.2454336</v>
       </c>
       <c r="N97">
-        <v>-100.830377</v>
+        <v>-102.1454336</v>
       </c>
       <c r="O97">
         <v>-0</v>
       </c>
       <c r="P97">
-        <v>-100.830377</v>
+        <v>-102.1454336</v>
       </c>
       <c r="Q97">
-        <v>-94.53037700000003</v>
+        <v>-95.84543360000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>1.248890074793917</v>
+        <v>1.549662593492397</v>
       </c>
       <c r="T97">
-        <v>23.45046486811206</v>
+        <v>29.31308108514009</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
@@ -9407,7 +9407,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.1929074463611039</v>
+        <v>0.1908979937948424</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9415,22 +9415,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2883545037396958</v>
+        <v>0.2902545037396957</v>
       </c>
       <c r="C98">
-        <v>-358.2169464258469</v>
+        <v>-364.7831799972946</v>
       </c>
       <c r="D98">
-        <v>127.2750535741531</v>
+        <v>126.2858200027054</v>
       </c>
       <c r="E98">
-        <v>512.292</v>
+        <v>517.869</v>
       </c>
       <c r="F98">
-        <v>535.3920000000001</v>
+        <v>540.9690000000001</v>
       </c>
       <c r="G98">
         <v>49.9</v>
@@ -9451,28 +9451,28 @@
         <v>24.1</v>
       </c>
       <c r="M98">
-        <v>126.2454336</v>
+        <v>127.5604902</v>
       </c>
       <c r="N98">
-        <v>-102.1454336</v>
+        <v>-103.4604902</v>
       </c>
       <c r="O98">
         <v>-0</v>
       </c>
       <c r="P98">
-        <v>-102.1454336</v>
+        <v>-103.4604902</v>
       </c>
       <c r="Q98">
-        <v>-95.84543360000002</v>
+        <v>-97.16049020000001</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.549662593492392</v>
+        <v>2.050950124656523</v>
       </c>
       <c r="T98">
-        <v>29.31308108514001</v>
+        <v>39.08410811352002</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
@@ -9489,7 +9489,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.1908979937948424</v>
+        <v>0.1889299732402565</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9497,22 +9497,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2902545037396957</v>
+        <v>0.2921545037396958</v>
       </c>
       <c r="C99">
-        <v>-364.7831799972946</v>
+        <v>-371.3341547140656</v>
       </c>
       <c r="D99">
-        <v>126.2858200027054</v>
+        <v>125.3118452859344</v>
       </c>
       <c r="E99">
-        <v>517.869</v>
+        <v>523.446</v>
       </c>
       <c r="F99">
-        <v>540.9690000000001</v>
+        <v>546.546</v>
       </c>
       <c r="G99">
         <v>49.9</v>
@@ -9533,28 +9533,28 @@
         <v>24.1</v>
       </c>
       <c r="M99">
-        <v>127.5604902</v>
+        <v>128.8755468</v>
       </c>
       <c r="N99">
-        <v>-103.4604902</v>
+        <v>-104.7755468</v>
       </c>
       <c r="O99">
         <v>-0</v>
       </c>
       <c r="P99">
-        <v>-103.4604902</v>
+        <v>-104.7755468</v>
       </c>
       <c r="Q99">
-        <v>-97.16049020000001</v>
+        <v>-98.47554680000003</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>2.050950124656523</v>
+        <v>3.053525186984785</v>
       </c>
       <c r="T99">
-        <v>39.08410811352002</v>
+        <v>58.62616217028002</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
@@ -9571,7 +9571,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.1889299732402565</v>
+        <v>0.1870021163704578</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9579,22 +9579,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2921545037396958</v>
+        <v>0.2940545037396958</v>
       </c>
       <c r="C100">
-        <v>-371.3341547140656</v>
+        <v>-377.8702209241712</v>
       </c>
       <c r="D100">
-        <v>125.3118452859344</v>
+        <v>124.3527790758288</v>
       </c>
       <c r="E100">
-        <v>523.446</v>
+        <v>529.023</v>
       </c>
       <c r="F100">
-        <v>546.546</v>
+        <v>552.123</v>
       </c>
       <c r="G100">
         <v>49.9</v>
@@ -9615,28 +9615,28 @@
         <v>24.1</v>
       </c>
       <c r="M100">
-        <v>128.8755468</v>
+        <v>130.1906034</v>
       </c>
       <c r="N100">
-        <v>-104.7755468</v>
+        <v>-106.0906034</v>
       </c>
       <c r="O100">
         <v>-0</v>
       </c>
       <c r="P100">
-        <v>-104.7755468</v>
+        <v>-106.0906034</v>
       </c>
       <c r="Q100">
-        <v>-98.47554680000003</v>
+        <v>-99.79060340000002</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>3.053525186984785</v>
+        <v>6.061250373969569</v>
       </c>
       <c r="T100">
-        <v>58.62616217028002</v>
+        <v>117.25232434056</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
@@ -9653,91 +9653,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.1870021163704578</v>
+        <v>0.1851132061040897</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2940545037396958</v>
-      </c>
-      <c r="C101">
-        <v>-377.8702209241712</v>
-      </c>
-      <c r="D101">
-        <v>124.3527790758288</v>
-      </c>
-      <c r="E101">
-        <v>529.023</v>
-      </c>
-      <c r="F101">
-        <v>552.123</v>
-      </c>
-      <c r="G101">
-        <v>49.9</v>
-      </c>
-      <c r="H101">
-        <v>534.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>30.4</v>
-      </c>
-      <c r="K101">
-        <v>6.299999999999997</v>
-      </c>
-      <c r="L101">
-        <v>24.1</v>
-      </c>
-      <c r="M101">
-        <v>130.1906034</v>
-      </c>
-      <c r="N101">
-        <v>-106.0906034</v>
-      </c>
-      <c r="O101">
-        <v>-0</v>
-      </c>
-      <c r="P101">
-        <v>-106.0906034</v>
-      </c>
-      <c r="Q101">
-        <v>-99.79060340000002</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>6.061250373969569</v>
-      </c>
-      <c r="T101">
-        <v>117.25232434056</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0</v>
-      </c>
-      <c r="W101">
-        <v>0.2358</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.1851132061040897</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
